--- a/data/modelamiento/interpretabilidad_modelos.xlsx
+++ b/data/modelamiento/interpretabilidad_modelos.xlsx
@@ -67614,7 +67614,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R115"/>
+  <dimension ref="A1:T115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -67695,15 +67695,25 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>importancia_norm_minmax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>score_combinado</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>estabilidad_consenso</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>prioridad_tesis</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ranking_consenso</t>
         </is>
@@ -67722,27 +67732,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>x_ju_maltose_consumption_g_l</t>
+          <t>x_gcfid_4_ethyl_guaiacol_ppm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ju maltose consumption g l</t>
+          <t>gcfid 4 ethyl guaiacol ppm</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JU</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>fermentacion_indirecta</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>media_indirecta</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H2">
@@ -67754,36 +67764,42 @@
         </is>
       </c>
       <c r="J2">
-        <v>0.9025000000000001</v>
+        <v>0.825</v>
       </c>
       <c r="K2">
+        <v>0.95</v>
+      </c>
+      <c r="L2">
+        <v>36.21920442171134</v>
+      </c>
+      <c r="M2">
+        <v>51.89013760839237</v>
+      </c>
+      <c r="N2">
+        <v>330</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P2">
         <v>1</v>
       </c>
-      <c r="L2">
-        <v>8.006378279693029</v>
-      </c>
-      <c r="M2">
-        <v>30.13008720070722</v>
-      </c>
-      <c r="N2">
-        <v>361</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2">
+        <v>0.9125</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R2">
+      <c r="T2">
         <v>1</v>
       </c>
     </row>
@@ -67851,17 +67867,23 @@
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3">
+        <v>0.8354031360649414</v>
+      </c>
+      <c r="Q3">
+        <v>0.8677015680324707</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>2</v>
       </c>
     </row>
@@ -67878,27 +67900,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>x_gcfid_4_ethyl_guaiacol_ppm</t>
+          <t>x_ju_maltose_consumption_g_l</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>gcfid 4 ethyl guaiacol ppm</t>
+          <t>ju maltose consumption g l</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>JU</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>fermentacion_indirecta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>media_indirecta</t>
         </is>
       </c>
       <c r="H4">
@@ -67910,36 +67932,42 @@
         </is>
       </c>
       <c r="J4">
-        <v>0.825</v>
+        <v>0.9025000000000001</v>
       </c>
       <c r="K4">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>36.21920442171134</v>
+        <v>8.006378279693029</v>
       </c>
       <c r="M4">
-        <v>51.89013760839237</v>
+        <v>30.13008720070722</v>
       </c>
       <c r="N4">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+          <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P4">
+        <v>0.2174170554261122</v>
+      </c>
+      <c r="Q4">
+        <v>0.5599585277130561</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>prioritaria</t>
-        </is>
-      </c>
-      <c r="R4">
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
+        </is>
+      </c>
+      <c r="T4">
         <v>3</v>
       </c>
     </row>
@@ -68007,17 +68035,23 @@
           <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5">
+        <v>0.2152059062818368</v>
+      </c>
+      <c r="Q5">
+        <v>0.4876029531409184</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>prioritaria</t>
-        </is>
-      </c>
-      <c r="R5">
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
+        </is>
+      </c>
+      <c r="T5">
         <v>4</v>
       </c>
     </row>
@@ -68034,27 +68068,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>x_gcfid_guaiacol_ppm</t>
+          <t>x_ju_ethanol_production_g_l</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>gcfid guaiacol ppm</t>
+          <t>ju ethanol production g l</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>JU</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>fermentacion_indirecta</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>media_indirecta</t>
         </is>
       </c>
       <c r="H6">
@@ -68066,36 +68100,42 @@
         </is>
       </c>
       <c r="J6">
-        <v>0.7524999999999999</v>
+        <v>0.6675</v>
       </c>
       <c r="K6">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="L6">
-        <v>3.178167395991517</v>
+        <v>7.855940633058448</v>
       </c>
       <c r="M6">
-        <v>4.341506335983394</v>
+        <v>27.99051361055944</v>
       </c>
       <c r="N6">
-        <v>301</v>
+        <v>267</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>prioritaria</t>
-        </is>
-      </c>
-      <c r="R6">
+          <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P6">
+        <v>0.2132441329444925</v>
+      </c>
+      <c r="Q6">
+        <v>0.4403720664722462</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
+        </is>
+      </c>
+      <c r="T6">
         <v>5</v>
       </c>
     </row>
@@ -68112,27 +68152,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>x_ju_ethanol_production_g_l</t>
+          <t>x_gcfid_guaiacol_ppm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ju ethanol production g l</t>
+          <t>gcfid guaiacol ppm</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JU</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>fermentacion_indirecta</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>media_indirecta</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H7">
@@ -68144,36 +68184,42 @@
         </is>
       </c>
       <c r="J7">
-        <v>0.6675</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="K7">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="L7">
-        <v>7.855940633058448</v>
+        <v>3.178167395991517</v>
       </c>
       <c r="M7">
-        <v>27.99051361055944</v>
+        <v>4.341506335983394</v>
       </c>
       <c r="N7">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P7">
+        <v>0.08348947683576985</v>
+      </c>
+      <c r="Q7">
+        <v>0.4179947384178849</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R7">
+      <c r="T7">
         <v>6</v>
       </c>
     </row>
@@ -68241,17 +68287,23 @@
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8">
+        <v>0.0485117596914657</v>
+      </c>
+      <c r="Q8">
+        <v>0.3455058798457329</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R8">
+      <c r="T8">
         <v>7</v>
       </c>
     </row>
@@ -68268,27 +68320,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>x_gcfid_p_cresol_ppm</t>
+          <t>x_ju_ethyl_myristate_ppm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>gcfid p cresol ppm</t>
+          <t>ju ethyl myristate ppm</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>JU</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>media_contextual</t>
         </is>
       </c>
       <c r="H9">
@@ -68300,36 +68352,42 @@
         </is>
       </c>
       <c r="J9">
-        <v>0.4275</v>
+        <v>0.14</v>
       </c>
       <c r="K9">
-        <v>0.68</v>
+        <v>0.25</v>
       </c>
       <c r="L9">
-        <v>6.040573385004692</v>
+        <v>22.65978633547522</v>
       </c>
       <c r="M9">
-        <v>8.450042272435599</v>
+        <v>36.84003470199482</v>
       </c>
       <c r="N9">
-        <v>171</v>
+        <v>56</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>baja_media</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P9">
+        <v>0.6238813765335185</v>
+      </c>
+      <c r="Q9">
+        <v>0.3819406882667593</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R9">
+      <c r="T9">
         <v>8</v>
       </c>
     </row>
@@ -68346,27 +68404,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>x_gcms_esteres_pct</t>
+          <t>x_gcfid_p_cresol_ppm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>gcms esteres pct</t>
+          <t>gcfid p cresol ppm</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GC-MS</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>media_contextual</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H10">
@@ -68378,36 +68436,42 @@
         </is>
       </c>
       <c r="J10">
-        <v>0.38</v>
+        <v>0.4275</v>
       </c>
       <c r="K10">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="L10">
-        <v>0.9335452803720912</v>
+        <v>6.040573385004692</v>
       </c>
       <c r="M10">
-        <v>2.076945046213609</v>
+        <v>8.450042272435599</v>
       </c>
       <c r="N10">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P10">
+        <v>0.1628884741631468</v>
+      </c>
+      <c r="Q10">
+        <v>0.2951942370815734</v>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>baja_media</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R10">
+      <c r="T10">
         <v>9</v>
       </c>
     </row>
@@ -68424,27 +68488,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>x_gcms_aldehidos_pct</t>
+          <t>x_ju_isoamyl_octanoate_ppm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>gcms aldehidos pct</t>
+          <t>ju isoamyl octanoate ppm</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GC-MS</t>
+          <t>JU</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>aldehidos_furanicos</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>baja_contextual</t>
+          <t>media_contextual</t>
         </is>
       </c>
       <c r="H11">
@@ -68456,36 +68520,42 @@
         </is>
       </c>
       <c r="J11">
-        <v>0.365</v>
+        <v>0.17</v>
       </c>
       <c r="K11">
-        <v>0.58</v>
+        <v>0.3</v>
       </c>
       <c r="L11">
-        <v>2.684140026361019</v>
+        <v>15.08895681625171</v>
       </c>
       <c r="M11">
-        <v>5.169297486791581</v>
+        <v>21.17685442390149</v>
       </c>
       <c r="N11">
-        <v>146</v>
+        <v>68</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>baja_media</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P11">
+        <v>0.4138775283477162</v>
+      </c>
+      <c r="Q11">
+        <v>0.2919387641738581</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R11">
+      <c r="T11">
         <v>10</v>
       </c>
     </row>
@@ -68502,27 +68572,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>x_gcms_aroma_fermentativo_pct</t>
+          <t>x_ju_ethyl_hexadecanoate_ppm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>gcms aroma fermentativo pct</t>
+          <t>ju ethyl hexadecanoate ppm</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GC-MS</t>
+          <t>JU</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>no_prioritaria</t>
+          <t>media_contextual</t>
         </is>
       </c>
       <c r="H12">
@@ -68534,36 +68604,42 @@
         </is>
       </c>
       <c r="J12">
-        <v>0.3625</v>
+        <v>0.2925</v>
       </c>
       <c r="K12">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="L12">
-        <v>0.8757130351753786</v>
+        <v>8.776388611724112</v>
       </c>
       <c r="M12">
-        <v>1.888027310985135</v>
+        <v>19.00100485954763</v>
       </c>
       <c r="N12">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>baja_media</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P12">
+        <v>0.2387760270498636</v>
+      </c>
+      <c r="Q12">
+        <v>0.2656380135249318</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R12">
+      <c r="T12">
         <v>11</v>
       </c>
     </row>
@@ -68580,27 +68656,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>x_ju_ethyl_octanoate_ppm</t>
+          <t>x_gcms_aldehidos_pct</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ju ethyl octanoate ppm</t>
+          <t>gcms aldehidos pct</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JU</t>
+          <t>GC-MS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>aldehidos_furanicos</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>media_contextual</t>
+          <t>baja_contextual</t>
         </is>
       </c>
       <c r="H13">
@@ -68612,36 +68688,42 @@
         </is>
       </c>
       <c r="J13">
-        <v>0.355</v>
+        <v>0.365</v>
       </c>
       <c r="K13">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="L13">
-        <v>0.2086841167441899</v>
+        <v>2.684140026361019</v>
       </c>
       <c r="M13">
-        <v>0.7676894018351726</v>
+        <v>5.169297486791581</v>
       </c>
       <c r="N13">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P13">
+        <v>0.06978587296144104</v>
+      </c>
+      <c r="Q13">
+        <v>0.2173929364807205</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>baja_media</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R13">
+      <c r="T13">
         <v>12</v>
       </c>
     </row>
@@ -68658,17 +68740,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_octanoate_ppm</t>
+          <t>x_gcms_esteres_pct</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>gcfid ethyl octanoate ppm</t>
+          <t>gcms esteres pct</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>GC-MS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -68690,36 +68772,42 @@
         </is>
       </c>
       <c r="J14">
-        <v>0.3525</v>
+        <v>0.38</v>
       </c>
       <c r="K14">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="L14">
-        <v>1.057737219493754</v>
+        <v>0.9335452803720912</v>
       </c>
       <c r="M14">
-        <v>4.126496645683983</v>
+        <v>2.076945046213609</v>
       </c>
       <c r="N14">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14">
+        <v>0.02122690959579555</v>
+      </c>
+      <c r="Q14">
+        <v>0.2006134547978978</v>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>baja_media</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R14">
+      <c r="T14">
         <v>13</v>
       </c>
     </row>
@@ -68787,17 +68875,23 @@
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15">
+        <v>0.04512295719430501</v>
+      </c>
+      <c r="Q15">
+        <v>0.1975614785971525</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>baja_media</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R15">
+      <c r="T15">
         <v>14</v>
       </c>
     </row>
@@ -68814,27 +68908,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>x_gcms_fenolicos_pct</t>
+          <t>x_gcfid_furfural_ppm</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>gcms fenolicos pct</t>
+          <t>gcfid furfural ppm</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GC-MS</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>aldehidos_furanicos</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>baja_contextual</t>
         </is>
       </c>
       <c r="H16">
@@ -68846,36 +68940,42 @@
         </is>
       </c>
       <c r="J16">
-        <v>0.3475</v>
+        <v>0.3325</v>
       </c>
       <c r="K16">
-        <v>0.57</v>
+        <v>0.48</v>
       </c>
       <c r="L16">
-        <v>1.450700232142892</v>
+        <v>2.324924159643433</v>
       </c>
       <c r="M16">
-        <v>2.500419842224819</v>
+        <v>5.652524584090574</v>
       </c>
       <c r="N16">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P16">
+        <v>0.059821744968789</v>
+      </c>
+      <c r="Q16">
+        <v>0.1961608724843945</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>baja_media</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R16">
+      <c r="T16">
         <v>15</v>
       </c>
     </row>
@@ -68892,27 +68992,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>x_gcfid_furfural_ppm</t>
+          <t>x_ju_ethyl_decanoate_ppm</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>gcfid furfural ppm</t>
+          <t>ju ethyl decanoate ppm</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>JU</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>aldehidos_furanicos</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>baja_contextual</t>
+          <t>media_contextual</t>
         </is>
       </c>
       <c r="H17">
@@ -68924,36 +69024,42 @@
         </is>
       </c>
       <c r="J17">
-        <v>0.3325</v>
+        <v>0.26</v>
       </c>
       <c r="K17">
-        <v>0.48</v>
+        <v>0.37</v>
       </c>
       <c r="L17">
-        <v>2.324924159643433</v>
+        <v>4.82111884948638</v>
       </c>
       <c r="M17">
-        <v>5.652524584090574</v>
+        <v>10.00174417707224</v>
       </c>
       <c r="N17">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>baja_media</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
+          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P17">
+        <v>0.1290625711367713</v>
+      </c>
+      <c r="Q17">
+        <v>0.1945312855683856</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R17">
+      <c r="T17">
         <v>16</v>
       </c>
     </row>
@@ -68970,27 +69076,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>x_ju_ethyl_hexadecanoate_ppm</t>
+          <t>x_gcms_fenolicos_pct</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ju ethyl hexadecanoate ppm</t>
+          <t>gcms fenolicos pct</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JU</t>
+          <t>GC-MS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>media_contextual</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H18">
@@ -69002,36 +69108,42 @@
         </is>
       </c>
       <c r="J18">
-        <v>0.2925</v>
+        <v>0.3475</v>
       </c>
       <c r="K18">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="L18">
-        <v>8.776388611724112</v>
+        <v>1.450700232142892</v>
       </c>
       <c r="M18">
-        <v>19.00100485954763</v>
+        <v>2.500419842224819</v>
       </c>
       <c r="N18">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P18">
+        <v>0.0355720391096021</v>
+      </c>
+      <c r="Q18">
+        <v>0.191536019554801</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>baja_media</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R18">
+      <c r="T18">
         <v>17</v>
       </c>
     </row>
@@ -69048,27 +69160,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>x_ju_ethyl_decanoate_ppm</t>
+          <t>x_gcms_aroma_fermentativo_pct</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ju ethyl decanoate ppm</t>
+          <t>gcms aroma fermentativo pct</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JU</t>
+          <t>GC-MS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>otros</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>media_contextual</t>
+          <t>no_prioritaria</t>
         </is>
       </c>
       <c r="H19">
@@ -69080,36 +69192,42 @@
         </is>
       </c>
       <c r="J19">
-        <v>0.26</v>
+        <v>0.3625</v>
       </c>
       <c r="K19">
-        <v>0.37</v>
+        <v>0.61</v>
       </c>
       <c r="L19">
-        <v>4.82111884948638</v>
+        <v>0.8757130351753786</v>
       </c>
       <c r="M19">
-        <v>10.00174417707224</v>
+        <v>1.888027310985135</v>
       </c>
       <c r="N19">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P19">
+        <v>0.01962272685601829</v>
+      </c>
+      <c r="Q19">
+        <v>0.1910613634280091</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>baja_media</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R19">
+      <c r="T19">
         <v>18</v>
       </c>
     </row>
@@ -69126,12 +69244,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_decanoate_ppm</t>
+          <t>x_gcfid_ethyl_octanoate_ppm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>gcfid ethyl decanoate ppm</t>
+          <t>gcfid ethyl octanoate ppm</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -69158,36 +69276,42 @@
         </is>
       </c>
       <c r="J20">
-        <v>0.1825</v>
+        <v>0.3525</v>
       </c>
       <c r="K20">
-        <v>0.28</v>
+        <v>0.6</v>
       </c>
       <c r="L20">
-        <v>0.9703553805348436</v>
+        <v>1.057737219493754</v>
       </c>
       <c r="M20">
-        <v>3.521554383782246</v>
+        <v>4.126496645683983</v>
       </c>
       <c r="N20">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
+      <c r="P20">
+        <v>0.02467181415519461</v>
+      </c>
+      <c r="Q20">
+        <v>0.1885859070775973</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>baja_media</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R20">
+      <c r="T20">
         <v>19</v>
       </c>
     </row>
@@ -69204,12 +69328,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>x_ju_isoamyl_octanoate_ppm</t>
+          <t>x_ju_ethyl_octanoate_ppm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ju isoamyl octanoate ppm</t>
+          <t>ju ethyl octanoate ppm</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -69236,36 +69360,42 @@
         </is>
       </c>
       <c r="J21">
-        <v>0.17</v>
+        <v>0.355</v>
       </c>
       <c r="K21">
-        <v>0.3</v>
+        <v>0.52</v>
       </c>
       <c r="L21">
-        <v>15.08895681625171</v>
+        <v>0.2086841167441899</v>
       </c>
       <c r="M21">
-        <v>21.17685442390149</v>
+        <v>0.7676894018351726</v>
       </c>
       <c r="N21">
-        <v>68</v>
+        <v>142</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="P21">
+        <v>0.001120310526858875</v>
+      </c>
+      <c r="Q21">
+        <v>0.1780601552634294</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>baja_media</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R21">
+      <c r="T21">
         <v>20</v>
       </c>
     </row>
@@ -69282,17 +69412,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_hexadecanoate_ppm</t>
+          <t>x_ju_ethyl_dodecanoate_ppm</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>gcfid ethyl hexadecanoate ppm</t>
+          <t>ju ethyl dodecanoate ppm</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>JU</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -69314,36 +69444,42 @@
         </is>
       </c>
       <c r="J22">
-        <v>0.1525</v>
+        <v>0.13</v>
       </c>
       <c r="K22">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="L22">
-        <v>0.4312565089105996</v>
+        <v>7.845226378796404</v>
       </c>
       <c r="M22">
-        <v>0.9588644063360804</v>
+        <v>15.17214648151355</v>
       </c>
       <c r="N22">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22">
+        <v>0.2129469350456682</v>
+      </c>
+      <c r="Q22">
+        <v>0.1714734675228341</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R22">
+      <c r="T22">
         <v>21</v>
       </c>
     </row>
@@ -69360,17 +69496,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>x_gcfid_isoamyl_acetate_ppm</t>
+          <t>x_ju_isoamyl_acetate_ppm</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>gcfid isoamyl acetate ppm</t>
+          <t>ju isoamyl acetate ppm</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>JU</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -69392,36 +69528,42 @@
         </is>
       </c>
       <c r="J23">
-        <v>0.145</v>
+        <v>0.1325</v>
       </c>
       <c r="K23">
         <v>0.23</v>
       </c>
       <c r="L23">
-        <v>1.067682617476174</v>
+        <v>5.894865681246315</v>
       </c>
       <c r="M23">
-        <v>2.09838346700016</v>
+        <v>12.52283825998301</v>
       </c>
       <c r="N23">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P23">
+        <v>0.158846753447883</v>
+      </c>
+      <c r="Q23">
+        <v>0.1456733767239415</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R23">
+      <c r="T23">
         <v>22</v>
       </c>
     </row>
@@ -69438,27 +69580,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>x_ju_ethyl_myristate_ppm</t>
+          <t>x_gcfid_creosol_ppm</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ju ethyl myristate ppm</t>
+          <t>gcfid creosol ppm</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>JU</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>otros</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>media_contextual</t>
+          <t>no_prioritaria</t>
         </is>
       </c>
       <c r="H24">
@@ -69470,36 +69612,42 @@
         </is>
       </c>
       <c r="J24">
-        <v>0.14</v>
+        <v>0.065</v>
       </c>
       <c r="K24">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="L24">
-        <v>22.65978633547522</v>
+        <v>8.033339119769989</v>
       </c>
       <c r="M24">
-        <v>36.84003470199482</v>
+        <v>9.817178184562572</v>
       </c>
       <c r="N24">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P24">
+        <v>0.2181649100901364</v>
+      </c>
+      <c r="Q24">
+        <v>0.1415824550450682</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R24">
+      <c r="T24">
         <v>23</v>
       </c>
     </row>
@@ -69516,12 +69664,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>x_ju_isoamyl_acetate_ppm</t>
+          <t>x_ju_ferulic_acid_conversion_index_faci_percent</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ju isoamyl acetate ppm</t>
+          <t>ju ferulic acid conversion index faci percent</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -69531,12 +69679,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>fermentacion_indirecta</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>media_contextual</t>
+          <t>media_indirecta</t>
         </is>
       </c>
       <c r="H25">
@@ -69548,36 +69696,42 @@
         </is>
       </c>
       <c r="J25">
-        <v>0.1325</v>
+        <v>0.1025</v>
       </c>
       <c r="K25">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="L25">
-        <v>5.894865681246315</v>
+        <v>6.46421875984568</v>
       </c>
       <c r="M25">
-        <v>12.52283825998301</v>
+        <v>19.33296104322974</v>
       </c>
       <c r="N25">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
+          <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P25">
+        <v>0.1746397834162244</v>
+      </c>
+      <c r="Q25">
+        <v>0.1385698917081122</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R25">
+      <c r="T25">
         <v>24</v>
       </c>
     </row>
@@ -69594,12 +69748,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>x_ju_ethyl_dodecanoate_ppm</t>
+          <t>x_ju_p_cresol_ppm</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ju ethyl dodecanoate ppm</t>
+          <t>ju p cresol ppm</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -69609,12 +69763,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>media_contextual</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H26">
@@ -69626,36 +69780,42 @@
         </is>
       </c>
       <c r="J26">
-        <v>0.13</v>
+        <v>0.0475</v>
       </c>
       <c r="K26">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="L26">
-        <v>7.845226378796404</v>
+        <v>7.197404139448359</v>
       </c>
       <c r="M26">
-        <v>15.17214648151355</v>
+        <v>10.90756031011137</v>
       </c>
       <c r="N26">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P26">
+        <v>0.1949772841827088</v>
+      </c>
+      <c r="Q26">
+        <v>0.1212386420913544</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R26">
+      <c r="T26">
         <v>25</v>
       </c>
     </row>
@@ -69672,27 +69832,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>x_ju_ferulic_acid_conversion_index_faci_percent</t>
+          <t>x_gcfid_ethyl_decanoate_ppm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ju ferulic acid conversion index faci percent</t>
+          <t>gcfid ethyl decanoate ppm</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>JU</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>fermentacion_indirecta</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>media_indirecta</t>
+          <t>media_contextual</t>
         </is>
       </c>
       <c r="H27">
@@ -69704,36 +69864,42 @@
         </is>
       </c>
       <c r="J27">
-        <v>0.1025</v>
+        <v>0.1825</v>
       </c>
       <c r="K27">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="L27">
-        <v>6.46421875984568</v>
+        <v>0.9703553805348436</v>
       </c>
       <c r="M27">
-        <v>19.33296104322974</v>
+        <v>3.521554383782246</v>
       </c>
       <c r="N27">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
+          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P27">
+        <v>0.02224796847271973</v>
+      </c>
+      <c r="Q27">
+        <v>0.1023739842363599</v>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R27">
+      <c r="T27">
         <v>26</v>
       </c>
     </row>
@@ -69750,12 +69916,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>x_gcfid_creosol_ppm</t>
+          <t>x_gcfid_isoamyl_acetate_ppm</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>gcfid creosol ppm</t>
+          <t>gcfid isoamyl acetate ppm</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -69765,12 +69931,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>no_prioritaria</t>
+          <t>media_contextual</t>
         </is>
       </c>
       <c r="H28">
@@ -69782,36 +69948,42 @@
         </is>
       </c>
       <c r="J28">
-        <v>0.065</v>
+        <v>0.145</v>
       </c>
       <c r="K28">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="L28">
-        <v>8.033339119769989</v>
+        <v>1.067682617476174</v>
       </c>
       <c r="M28">
-        <v>9.817178184562572</v>
+        <v>2.09838346700016</v>
       </c>
       <c r="N28">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
+          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P28">
+        <v>0.02494768509413786</v>
+      </c>
+      <c r="Q28">
+        <v>0.08497384254706893</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R28">
+      <c r="T28">
         <v>27</v>
       </c>
     </row>
@@ -69828,27 +70000,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>x_ju_p_cresol_ppm</t>
+          <t>x_gcfid_ethyl_hexadecanoate_ppm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ju p cresol ppm</t>
+          <t>gcfid ethyl hexadecanoate ppm</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>JU</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>media_contextual</t>
         </is>
       </c>
       <c r="H29">
@@ -69860,36 +70032,42 @@
         </is>
       </c>
       <c r="J29">
-        <v>0.0475</v>
+        <v>0.1525</v>
       </c>
       <c r="K29">
-        <v>0.1</v>
+        <v>0.23</v>
       </c>
       <c r="L29">
-        <v>7.197404139448359</v>
+        <v>0.4312565089105996</v>
       </c>
       <c r="M29">
-        <v>10.90756031011137</v>
+        <v>0.9588644063360804</v>
       </c>
       <c r="N29">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
+          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P29">
+        <v>0.007294146397311742</v>
+      </c>
+      <c r="Q29">
+        <v>0.07989707319865587</v>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R29">
+      <c r="T29">
         <v>28</v>
       </c>
     </row>
@@ -69906,12 +70084,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_dodecanoate_ppm</t>
+          <t>x_gcfid_isoamyl_octanoate_ppm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>gcfid ethyl dodecanoate ppm</t>
+          <t>gcfid isoamyl octanoate ppm</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -69930,44 +70108,50 @@
         </is>
       </c>
       <c r="H30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>elastic_net; lasso; random_forest_restringido; ridge</t>
+          <t>elastic_net; lasso; ridge</t>
         </is>
       </c>
       <c r="J30">
-        <v>0.0375</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="K30">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="L30">
-        <v>0.2064638774643513</v>
+        <v>4.589530588019777</v>
       </c>
       <c r="M30">
-        <v>0.579165857729705</v>
+        <v>6.453309054507804</v>
       </c>
       <c r="N30">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P30">
+        <v>0.1226386481070483</v>
+      </c>
+      <c r="Q30">
+        <v>0.07798599072019081</v>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R30">
+      <c r="T30">
         <v>29</v>
       </c>
     </row>
@@ -69984,12 +70168,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>x_gcfid_isoamyl_octanoate_ppm</t>
+          <t>x_gcfid_ethyl_dodecanoate_ppm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>gcfid isoamyl octanoate ppm</t>
+          <t>gcfid ethyl dodecanoate ppm</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -70008,44 +70192,50 @@
         </is>
       </c>
       <c r="H31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>elastic_net; lasso; ridge</t>
+          <t>elastic_net; lasso; random_forest_restringido; ridge</t>
         </is>
       </c>
       <c r="J31">
-        <v>0.03333333333333333</v>
+        <v>0.0375</v>
       </c>
       <c r="K31">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="L31">
-        <v>4.589530588019777</v>
+        <v>0.2064638774643513</v>
       </c>
       <c r="M31">
-        <v>6.453309054507804</v>
+        <v>0.579165857729705</v>
       </c>
       <c r="N31">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P31">
+        <v>0.00105872430417674</v>
+      </c>
+      <c r="Q31">
+        <v>0.01927936215208837</v>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R31">
+      <c r="T31">
         <v>30</v>
       </c>
     </row>
@@ -70113,17 +70303,23 @@
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R32">
+      <c r="T32">
         <v>31</v>
       </c>
     </row>
@@ -70140,12 +70336,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>x_gcfid_isoamyl_octanoate_ppm</t>
+          <t>x_gcfid_p_cresol_ppm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>gcfid isoamyl octanoate ppm</t>
+          <t>gcfid p cresol ppm</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -70155,12 +70351,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>baja_no_directa</t>
         </is>
       </c>
       <c r="H33">
@@ -70172,36 +70368,42 @@
         </is>
       </c>
       <c r="J33">
-        <v>0.825</v>
+        <v>0.5725</v>
       </c>
       <c r="K33">
         <v>0.99</v>
       </c>
       <c r="L33">
-        <v>32.82589280767829</v>
+        <v>52.71689767913747</v>
       </c>
       <c r="M33">
-        <v>62.75393563038882</v>
+        <v>73.41461117411556</v>
       </c>
       <c r="N33">
-        <v>330</v>
+        <v>229</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P33">
+        <v>1</v>
+      </c>
+      <c r="Q33">
+        <v>0.78625</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R33">
+      <c r="T33">
         <v>1</v>
       </c>
     </row>
@@ -70218,12 +70420,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_dodecanoate_ppm</t>
+          <t>x_gcfid_isoamyl_octanoate_ppm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>gcfid ethyl dodecanoate ppm</t>
+          <t>gcfid isoamyl octanoate ppm</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -70250,36 +70452,42 @@
         </is>
       </c>
       <c r="J34">
-        <v>0.765</v>
+        <v>0.825</v>
       </c>
       <c r="K34">
         <v>0.99</v>
       </c>
       <c r="L34">
-        <v>3.051559817866079</v>
+        <v>32.82589280767829</v>
       </c>
       <c r="M34">
-        <v>10.92686977437846</v>
+        <v>62.75393563038882</v>
       </c>
       <c r="N34">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
           <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P34">
+        <v>0.6045955522505274</v>
+      </c>
+      <c r="Q34">
+        <v>0.7147977761252637</v>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R34">
+      <c r="T34">
         <v>2</v>
       </c>
     </row>
@@ -70296,12 +70504,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_decanoate_ppm</t>
+          <t>x_gcfid_creosol_ppm</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>gcfid ethyl decanoate ppm</t>
+          <t>gcfid creosol ppm</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -70311,12 +70519,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>otros</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>no_prioritaria</t>
         </is>
       </c>
       <c r="H35">
@@ -70328,36 +70536,42 @@
         </is>
       </c>
       <c r="J35">
-        <v>0.7325</v>
+        <v>0.5925</v>
       </c>
       <c r="K35">
         <v>0.99</v>
       </c>
       <c r="L35">
-        <v>4.716021844570279</v>
+        <v>22.74754975381472</v>
       </c>
       <c r="M35">
-        <v>11.82841628602838</v>
+        <v>36.77977778998949</v>
       </c>
       <c r="N35">
-        <v>293</v>
+        <v>237</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P35">
+        <v>0.4042526487524437</v>
+      </c>
+      <c r="Q35">
+        <v>0.4983763243762218</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R35">
+      <c r="T35">
         <v>3</v>
       </c>
     </row>
@@ -70425,17 +70639,23 @@
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P36">
+        <v>0.1413057717502346</v>
+      </c>
+      <c r="Q36">
+        <v>0.4231528858751173</v>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R36">
+      <c r="T36">
         <v>4</v>
       </c>
     </row>
@@ -70452,12 +70672,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>x_gcfid_creosol_ppm</t>
+          <t>x_gcfid_ethyl_decanoate_ppm</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>gcfid creosol ppm</t>
+          <t>gcfid ethyl decanoate ppm</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -70467,12 +70687,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>no_prioritaria</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H37">
@@ -70484,36 +70704,42 @@
         </is>
       </c>
       <c r="J37">
-        <v>0.5925</v>
+        <v>0.7325</v>
       </c>
       <c r="K37">
         <v>0.99</v>
       </c>
       <c r="L37">
-        <v>22.74754975381472</v>
+        <v>4.716021844570279</v>
       </c>
       <c r="M37">
-        <v>36.77977778998949</v>
+        <v>11.82841628602838</v>
       </c>
       <c r="N37">
-        <v>237</v>
+        <v>293</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
+          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
+        </is>
+      </c>
+      <c r="P37">
+        <v>0.04581191732091151</v>
+      </c>
+      <c r="Q37">
+        <v>0.3891559586604558</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R37">
+      <c r="T37">
         <v>5</v>
       </c>
     </row>
@@ -70530,12 +70756,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_hexadecanoate_ppm</t>
+          <t>x_gcfid_ethyl_dodecanoate_ppm</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>gcfid ethyl hexadecanoate ppm</t>
+          <t>gcfid ethyl dodecanoate ppm</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -70562,36 +70788,42 @@
         </is>
       </c>
       <c r="J38">
-        <v>0.5825</v>
+        <v>0.765</v>
       </c>
       <c r="K38">
         <v>0.99</v>
       </c>
       <c r="L38">
-        <v>3.647709374887292</v>
+        <v>3.051559817866079</v>
       </c>
       <c r="M38">
-        <v>11.117427736486</v>
+        <v>10.92686977437846</v>
       </c>
       <c r="N38">
-        <v>233</v>
+        <v>306</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
+      <c r="P38">
+        <v>0.01272481625578255</v>
+      </c>
+      <c r="Q38">
+        <v>0.3888624081278913</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R38">
+      <c r="T38">
         <v>6</v>
       </c>
     </row>
@@ -70659,17 +70891,23 @@
           <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P39">
+        <v>0.1242405258704185</v>
+      </c>
+      <c r="Q39">
+        <v>0.3521202629352093</v>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R39">
+      <c r="T39">
         <v>7</v>
       </c>
     </row>
@@ -70686,17 +70924,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>x_gcfid_p_cresol_ppm</t>
+          <t>x_gcms_fenolicos_pct</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>gcfid p cresol ppm</t>
+          <t>gcms fenolicos pct</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>GC-MS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -70718,36 +70956,42 @@
         </is>
       </c>
       <c r="J40">
-        <v>0.5725</v>
+        <v>0.27</v>
       </c>
       <c r="K40">
-        <v>0.99</v>
+        <v>0.43</v>
       </c>
       <c r="L40">
-        <v>52.71689767913747</v>
+        <v>22.2308714250324</v>
       </c>
       <c r="M40">
-        <v>73.41461117411556</v>
+        <v>37.04439601895355</v>
       </c>
       <c r="N40">
-        <v>229</v>
+        <v>108</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
+      <c r="P40">
+        <v>0.3939818298281855</v>
+      </c>
+      <c r="Q40">
+        <v>0.3319909149140928</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R40">
+      <c r="T40">
         <v>8</v>
       </c>
     </row>
@@ -70764,12 +71008,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_tetradecanoate_ppm</t>
+          <t>x_gcfid_ethyl_hexadecanoate_ppm</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>gcfid ethyl tetradecanoate ppm</t>
+          <t>gcfid ethyl hexadecanoate ppm</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -70796,36 +71040,42 @@
         </is>
       </c>
       <c r="J41">
-        <v>0.54</v>
+        <v>0.5825</v>
       </c>
       <c r="K41">
         <v>0.99</v>
       </c>
       <c r="L41">
-        <v>4.18154839143308</v>
+        <v>3.647709374887292</v>
       </c>
       <c r="M41">
-        <v>9.892033587041931</v>
+        <v>11.117427736486</v>
       </c>
       <c r="N41">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
           <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P41">
+        <v>0.02457540841507016</v>
+      </c>
+      <c r="Q41">
+        <v>0.3035377042075351</v>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R41">
+      <c r="T41">
         <v>9</v>
       </c>
     </row>
@@ -70842,27 +71092,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_octanoate_ppm</t>
+          <t>x_gcms_aldehidos_pct</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>gcfid ethyl octanoate ppm</t>
+          <t>gcms aldehidos pct</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>GC-MS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>aldehidos_furanicos</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>no_prioritaria</t>
         </is>
       </c>
       <c r="H42">
@@ -70874,36 +71124,42 @@
         </is>
       </c>
       <c r="J42">
-        <v>0.535</v>
+        <v>0.2225</v>
       </c>
       <c r="K42">
-        <v>0.99</v>
+        <v>0.43</v>
       </c>
       <c r="L42">
-        <v>2.411432010572006</v>
+        <v>20.51607932715576</v>
       </c>
       <c r="M42">
-        <v>9.272461496576501</v>
+        <v>33.68746170754822</v>
       </c>
       <c r="N42">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P42">
+        <v>0.359894239641178</v>
+      </c>
+      <c r="Q42">
+        <v>0.291197119820589</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R42">
+      <c r="T42">
         <v>10</v>
       </c>
     </row>
@@ -70920,27 +71176,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>x_gcms_aroma_fermentativo_pct</t>
+          <t>x_gcfid_ethyl_tetradecanoate_ppm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>gcms aroma fermentativo pct</t>
+          <t>gcfid ethyl tetradecanoate ppm</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GC-MS</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>no_prioritaria</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H43">
@@ -70952,36 +71208,42 @@
         </is>
       </c>
       <c r="J43">
-        <v>0.285</v>
+        <v>0.54</v>
       </c>
       <c r="K43">
-        <v>0.43</v>
+        <v>0.99</v>
       </c>
       <c r="L43">
-        <v>5.553161330998145</v>
+        <v>4.18154839143308</v>
       </c>
       <c r="M43">
-        <v>15.19788108854277</v>
+        <v>9.892033587041931</v>
       </c>
       <c r="N43">
-        <v>114</v>
+        <v>216</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
+          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
+        </is>
+      </c>
+      <c r="P43">
+        <v>0.03518735702643883</v>
+      </c>
+      <c r="Q43">
+        <v>0.2875936785132194</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R43">
+      <c r="T43">
         <v>11</v>
       </c>
     </row>
@@ -70998,27 +71260,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>x_gcms_fenolicos_pct</t>
+          <t>x_gcfid_ethyl_octanoate_ppm</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>gcms fenolicos pct</t>
+          <t>gcfid ethyl octanoate ppm</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>GC-MS</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>baja_no_directa</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H44">
@@ -71030,36 +71292,42 @@
         </is>
       </c>
       <c r="J44">
-        <v>0.27</v>
+        <v>0.535</v>
       </c>
       <c r="K44">
-        <v>0.43</v>
+        <v>0.99</v>
       </c>
       <c r="L44">
-        <v>22.2308714250324</v>
+        <v>2.411432010572006</v>
       </c>
       <c r="M44">
-        <v>37.04439601895355</v>
+        <v>9.272461496576501</v>
       </c>
       <c r="N44">
-        <v>108</v>
+        <v>214</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
+          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
+        </is>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0.2675</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R44">
+      <c r="T44">
         <v>12</v>
       </c>
     </row>
@@ -71076,12 +71344,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>x_gcms_esteres_pct</t>
+          <t>x_gcms_aroma_fermentativo_pct</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>gcms esteres pct</t>
+          <t>gcms aroma fermentativo pct</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -71091,12 +71359,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>otros</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>no_prioritaria</t>
         </is>
       </c>
       <c r="H45">
@@ -71108,36 +71376,42 @@
         </is>
       </c>
       <c r="J45">
-        <v>0.265</v>
+        <v>0.285</v>
       </c>
       <c r="K45">
         <v>0.43</v>
       </c>
       <c r="L45">
-        <v>3.477782562125795</v>
+        <v>5.553161330998145</v>
       </c>
       <c r="M45">
-        <v>11.0419707716384</v>
+        <v>15.19788108854277</v>
       </c>
       <c r="N45">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P45">
+        <v>0.06245304120878701</v>
+      </c>
+      <c r="Q45">
+        <v>0.1737265206043935</v>
+      </c>
+      <c r="R45" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R45">
+      <c r="T45">
         <v>13</v>
       </c>
     </row>
@@ -71154,12 +71428,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>x_gcms_aldehidos_pct</t>
+          <t>x_gcms_esteres_pct</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>gcms aldehidos pct</t>
+          <t>gcms esteres pct</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -71169,12 +71443,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>aldehidos_furanicos</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>no_prioritaria</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H46">
@@ -71186,36 +71460,42 @@
         </is>
       </c>
       <c r="J46">
-        <v>0.2225</v>
+        <v>0.265</v>
       </c>
       <c r="K46">
         <v>0.43</v>
       </c>
       <c r="L46">
-        <v>20.51607932715576</v>
+        <v>3.477782562125795</v>
       </c>
       <c r="M46">
-        <v>33.68746170754822</v>
+        <v>11.0419707716384</v>
       </c>
       <c r="N46">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
+          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
+        </is>
+      </c>
+      <c r="P46">
+        <v>0.02119750880708224</v>
+      </c>
+      <c r="Q46">
+        <v>0.1430987544035411</v>
+      </c>
+      <c r="R46" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R46">
+      <c r="T46">
         <v>14</v>
       </c>
     </row>
@@ -71232,12 +71512,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>x_gcfid_guaiacol_ppm</t>
+          <t>x_gcfid_4_ethyl_guaiacol_ppm</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>gcfid guaiacol ppm</t>
+          <t>gcfid 4 ethyl guaiacol ppm</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -71264,36 +71544,42 @@
         </is>
       </c>
       <c r="J47">
-        <v>0.9199999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="K47">
         <v>0.99</v>
       </c>
       <c r="L47">
-        <v>9.104785529088867</v>
+        <v>30.19351235352796</v>
       </c>
       <c r="M47">
-        <v>12.54797176629789</v>
+        <v>38.05975554831253</v>
       </c>
       <c r="N47">
-        <v>368</v>
+        <v>328</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P47">
+        <v>1</v>
+      </c>
+      <c r="Q47">
+        <v>0.9099999999999999</v>
+      </c>
+      <c r="R47" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R47">
+      <c r="T47">
         <v>1</v>
       </c>
     </row>
@@ -71310,12 +71596,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>x_gcfid_p_cresol_ppm</t>
+          <t>x_gcfid_o_cresol_ppm</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>gcfid p cresol ppm</t>
+          <t>gcfid o cresol ppm</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -71342,36 +71628,42 @@
         </is>
       </c>
       <c r="J48">
-        <v>0.885</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="K48">
         <v>1</v>
       </c>
       <c r="L48">
-        <v>14.36146613171803</v>
+        <v>27.27993280578624</v>
       </c>
       <c r="M48">
-        <v>15.51945690575356</v>
+        <v>37.55698516790714</v>
       </c>
       <c r="N48">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="P48">
+        <v>0.8983713516897766</v>
+      </c>
+      <c r="Q48">
+        <v>0.8854356758448882</v>
+      </c>
+      <c r="R48" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R48">
+      <c r="T48">
         <v>2</v>
       </c>
     </row>
@@ -71388,12 +71680,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>x_gcfid_o_cresol_ppm</t>
+          <t>x_gcfid_p_cresol_ppm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>gcfid o cresol ppm</t>
+          <t>gcfid p cresol ppm</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -71420,36 +71712,42 @@
         </is>
       </c>
       <c r="J49">
-        <v>0.8725000000000001</v>
+        <v>0.885</v>
       </c>
       <c r="K49">
         <v>1</v>
       </c>
       <c r="L49">
-        <v>27.27993280578624</v>
+        <v>14.36146613171803</v>
       </c>
       <c r="M49">
-        <v>37.55698516790714</v>
+        <v>15.51945690575356</v>
       </c>
       <c r="N49">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P49">
+        <v>0.4477619604535488</v>
+      </c>
+      <c r="Q49">
+        <v>0.6663809802267744</v>
+      </c>
+      <c r="R49" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R49">
+      <c r="T49">
         <v>3</v>
       </c>
     </row>
@@ -71466,12 +71764,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>x_gcfid_4_ethyl_guaiacol_ppm</t>
+          <t>x_gcfid_guaiacol_ppm</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>gcfid 4 ethyl guaiacol ppm</t>
+          <t>gcfid guaiacol ppm</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -71498,36 +71796,42 @@
         </is>
       </c>
       <c r="J50">
-        <v>0.82</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="K50">
         <v>0.99</v>
       </c>
       <c r="L50">
-        <v>30.19351235352796</v>
+        <v>9.104785529088867</v>
       </c>
       <c r="M50">
-        <v>38.05975554831253</v>
+        <v>12.54797176629789</v>
       </c>
       <c r="N50">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="P50">
+        <v>0.2644035398269876</v>
+      </c>
+      <c r="Q50">
+        <v>0.5922017699134938</v>
+      </c>
+      <c r="R50" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>prioritaria</t>
-        </is>
-      </c>
-      <c r="R50">
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
+        </is>
+      </c>
+      <c r="T50">
         <v>4</v>
       </c>
     </row>
@@ -71544,12 +71848,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_decanoate_ppm</t>
+          <t>x_gcfid_furfural_ppm</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>gcfid ethyl decanoate ppm</t>
+          <t>gcfid furfural ppm</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -71559,12 +71863,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>aldehidos_furanicos</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>media_contextual</t>
+          <t>baja_contextual</t>
         </is>
       </c>
       <c r="H51">
@@ -71576,36 +71880,42 @@
         </is>
       </c>
       <c r="J51">
-        <v>0.7975</v>
+        <v>0.92</v>
       </c>
       <c r="K51">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="L51">
-        <v>2.625033083494357</v>
+        <v>6.49239254171642</v>
       </c>
       <c r="M51">
-        <v>10.13457060176403</v>
+        <v>15.96184756132217</v>
       </c>
       <c r="N51">
-        <v>319</v>
+        <v>368</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P51">
+        <v>0.1732805882097753</v>
+      </c>
+      <c r="Q51">
+        <v>0.5466402941048877</v>
+      </c>
+      <c r="R51" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>prioritaria</t>
-        </is>
-      </c>
-      <c r="R51">
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
+        </is>
+      </c>
+      <c r="T51">
         <v>5</v>
       </c>
     </row>
@@ -71622,27 +71932,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_octanoate_ppm</t>
+          <t>x_gcms_area_valida_pct</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>gcfid ethyl octanoate ppm</t>
+          <t>gcms area valida pct</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>GC-MS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>calidad_senal_analitica</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>media_contextual</t>
+          <t>baja_contextual</t>
         </is>
       </c>
       <c r="H52">
@@ -71654,36 +71964,42 @@
         </is>
       </c>
       <c r="J52">
-        <v>0.7475000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="K52">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="L52">
-        <v>3.570739258784272</v>
+        <v>3.548361772464024</v>
       </c>
       <c r="M52">
-        <v>14.18603562774937</v>
+        <v>7.907471817441999</v>
       </c>
       <c r="N52">
-        <v>299</v>
+        <v>348</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P52">
+        <v>0.07058977000481745</v>
+      </c>
+      <c r="Q52">
+        <v>0.4702948850024087</v>
+      </c>
+      <c r="R52" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>prioritaria</t>
-        </is>
-      </c>
-      <c r="R52">
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
+        </is>
+      </c>
+      <c r="T52">
         <v>6</v>
       </c>
     </row>
@@ -71700,12 +72016,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>x_gcfid_furfural_ppm</t>
+          <t>x_gcfid_ethyl_decanoate_ppm</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>gcfid furfural ppm</t>
+          <t>gcfid ethyl decanoate ppm</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -71715,12 +72031,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>aldehidos_furanicos</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>baja_contextual</t>
+          <t>media_contextual</t>
         </is>
       </c>
       <c r="H53">
@@ -71732,36 +72048,42 @@
         </is>
       </c>
       <c r="J53">
-        <v>0.92</v>
+        <v>0.7975</v>
       </c>
       <c r="K53">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="L53">
-        <v>6.49239254171642</v>
+        <v>2.625033083494357</v>
       </c>
       <c r="M53">
-        <v>15.96184756132217</v>
+        <v>10.13457060176403</v>
       </c>
       <c r="N53">
-        <v>368</v>
+        <v>319</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
+          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P53">
+        <v>0.03838311661902965</v>
+      </c>
+      <c r="Q53">
+        <v>0.4179415583095148</v>
+      </c>
+      <c r="R53" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R53">
+      <c r="T53">
         <v>7</v>
       </c>
     </row>
@@ -71778,27 +72100,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>x_gcms_area_valida_pct</t>
+          <t>x_gcfid_creosol_ppm</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>gcms area valida pct</t>
+          <t>gcfid creosol ppm</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>GC-MS</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>calidad_senal_analitica</t>
+          <t>otros</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>baja_contextual</t>
+          <t>no_prioritaria</t>
         </is>
       </c>
       <c r="H54">
@@ -71810,36 +72132,42 @@
         </is>
       </c>
       <c r="J54">
-        <v>0.87</v>
+        <v>0.62</v>
       </c>
       <c r="K54">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="L54">
-        <v>3.548361772464024</v>
+        <v>7.708468000297144</v>
       </c>
       <c r="M54">
-        <v>7.907471817441999</v>
+        <v>8.81420653978196</v>
       </c>
       <c r="N54">
-        <v>348</v>
+        <v>248</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
+      <c r="P54">
+        <v>0.2156985497150946</v>
+      </c>
+      <c r="Q54">
+        <v>0.4178492748575473</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R54">
+      <c r="T54">
         <v>8</v>
       </c>
     </row>
@@ -71856,12 +72184,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_hexadecanoate_ppm</t>
+          <t>x_gcfid_ethyl_octanoate_ppm</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>gcfid ethyl hexadecanoate ppm</t>
+          <t>gcfid ethyl octanoate ppm</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -71888,36 +72216,42 @@
         </is>
       </c>
       <c r="J55">
-        <v>0.6875</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="K55">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="L55">
-        <v>4.561414849918031</v>
+        <v>3.570739258784272</v>
       </c>
       <c r="M55">
-        <v>17.89867182274859</v>
+        <v>14.18603562774937</v>
       </c>
       <c r="N55">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
+      <c r="P55">
+        <v>0.07137031972039669</v>
+      </c>
+      <c r="Q55">
+        <v>0.4094351598601983</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R55">
+      <c r="T55">
         <v>9</v>
       </c>
     </row>
@@ -71934,12 +72268,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>x_gcms_fenolicos_pct</t>
+          <t>x_gcms_aldehidos_pct</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>gcms fenolicos pct</t>
+          <t>gcms aldehidos pct</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -71949,12 +72283,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>aldehidos_furanicos</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>baja_contextual</t>
         </is>
       </c>
       <c r="H56">
@@ -71966,36 +72300,42 @@
         </is>
       </c>
       <c r="J56">
-        <v>0.6825</v>
+        <v>0.605</v>
       </c>
       <c r="K56">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="L56">
-        <v>3.892702865650325</v>
+        <v>7.268886022126257</v>
       </c>
       <c r="M56">
-        <v>5.936844391353731</v>
+        <v>11.14064761695767</v>
       </c>
       <c r="N56">
-        <v>273</v>
+        <v>242</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P56">
+        <v>0.2003654786487262</v>
+      </c>
+      <c r="Q56">
+        <v>0.402682739324363</v>
+      </c>
+      <c r="R56" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R56">
+      <c r="T56">
         <v>10</v>
       </c>
     </row>
@@ -72063,17 +72403,23 @@
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="P57">
+        <v>0.1348456694757292</v>
+      </c>
+      <c r="Q57">
+        <v>0.3999228347378646</v>
+      </c>
+      <c r="R57" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R57">
+      <c r="T57">
         <v>11</v>
       </c>
     </row>
@@ -72090,27 +72436,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>x_gcms_aroma_fermentativo_pct</t>
+          <t>x_gcfid_ethyl_hexadecanoate_ppm</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>gcms aroma fermentativo pct</t>
+          <t>gcfid ethyl hexadecanoate ppm</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>GC-MS</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>no_prioritaria</t>
+          <t>media_contextual</t>
         </is>
       </c>
       <c r="H58">
@@ -72122,36 +72468,42 @@
         </is>
       </c>
       <c r="J58">
-        <v>0.6625000000000001</v>
+        <v>0.6875</v>
       </c>
       <c r="K58">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="L58">
-        <v>1.592445645790625</v>
+        <v>4.561414849918031</v>
       </c>
       <c r="M58">
-        <v>4.559008201581211</v>
+        <v>17.89867182274859</v>
       </c>
       <c r="N58">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
+          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P58">
+        <v>0.1059261022521941</v>
+      </c>
+      <c r="Q58">
+        <v>0.3967130511260971</v>
+      </c>
+      <c r="R58" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R58">
+      <c r="T58">
         <v>12</v>
       </c>
     </row>
@@ -72168,12 +72520,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>x_gcms_esteres_pct</t>
+          <t>x_gcms_fenolicos_pct</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>gcms esteres pct</t>
+          <t>gcms fenolicos pct</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -72183,12 +72535,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>media_contextual</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H59">
@@ -72200,36 +72552,42 @@
         </is>
       </c>
       <c r="J59">
-        <v>0.625</v>
+        <v>0.6825</v>
       </c>
       <c r="K59">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="L59">
-        <v>1.524632109760849</v>
+        <v>3.892702865650325</v>
       </c>
       <c r="M59">
-        <v>4.420323474564865</v>
+        <v>5.936844391353731</v>
       </c>
       <c r="N59">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P59">
+        <v>0.08260074114350234</v>
+      </c>
+      <c r="Q59">
+        <v>0.3825503705717512</v>
+      </c>
+      <c r="R59" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R59">
+      <c r="T59">
         <v>13</v>
       </c>
     </row>
@@ -72246,17 +72604,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>x_gcfid_creosol_ppm</t>
+          <t>x_gcms_aroma_fermentativo_pct</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>gcfid creosol ppm</t>
+          <t>gcms aroma fermentativo pct</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>GC-MS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -72278,36 +72636,42 @@
         </is>
       </c>
       <c r="J60">
-        <v>0.62</v>
+        <v>0.6625000000000001</v>
       </c>
       <c r="K60">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="L60">
-        <v>7.708468000297144</v>
+        <v>1.592445645790625</v>
       </c>
       <c r="M60">
-        <v>8.81420653978196</v>
+        <v>4.559008201581211</v>
       </c>
       <c r="N60">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="P60">
+        <v>0.002365405814708077</v>
+      </c>
+      <c r="Q60">
+        <v>0.3324327029073541</v>
+      </c>
+      <c r="R60" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R60">
+      <c r="T60">
         <v>14</v>
       </c>
     </row>
@@ -72324,12 +72688,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>x_gcms_aldehidos_pct</t>
+          <t>x_gcms_esteres_pct</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>gcms aldehidos pct</t>
+          <t>gcms esteres pct</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -72339,12 +72703,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>aldehidos_furanicos</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>baja_contextual</t>
+          <t>media_contextual</t>
         </is>
       </c>
       <c r="H61">
@@ -72356,36 +72720,42 @@
         </is>
       </c>
       <c r="J61">
-        <v>0.605</v>
+        <v>0.625</v>
       </c>
       <c r="K61">
-        <v>0.74</v>
+        <v>0.92</v>
       </c>
       <c r="L61">
-        <v>7.268886022126257</v>
+        <v>1.524632109760849</v>
       </c>
       <c r="M61">
-        <v>11.14064761695767</v>
+        <v>4.420323474564865</v>
       </c>
       <c r="N61">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
+          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>0.3125</v>
+      </c>
+      <c r="R61" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R61">
+      <c r="T61">
         <v>15</v>
       </c>
     </row>
@@ -72453,17 +72823,23 @@
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="P62">
+        <v>0.2245112607249574</v>
+      </c>
+      <c r="Q62">
+        <v>0.2872556303624787</v>
+      </c>
+      <c r="R62" t="inlineStr">
         <is>
           <t>baja_media</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R62">
+      <c r="T62">
         <v>16</v>
       </c>
     </row>
@@ -72480,12 +72856,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_tetradecanoate_ppm</t>
+          <t>x_gcfid_ethyl_dodecanoate_ppm</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>gcfid ethyl tetradecanoate ppm</t>
+          <t>gcfid ethyl dodecanoate ppm</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -72512,36 +72888,42 @@
         </is>
       </c>
       <c r="J63">
-        <v>0.1575</v>
+        <v>0.1125</v>
       </c>
       <c r="K63">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="L63">
-        <v>1.635576802586092</v>
+        <v>5.027298710393142</v>
       </c>
       <c r="M63">
-        <v>3.618990072475083</v>
+        <v>20.0772216256404</v>
       </c>
       <c r="N63">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="P63">
+        <v>0.1221766099983555</v>
+      </c>
+      <c r="Q63">
+        <v>0.1173383049991777</v>
+      </c>
+      <c r="R63" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R63">
+      <c r="T63">
         <v>17</v>
       </c>
     </row>
@@ -72558,12 +72940,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_dodecanoate_ppm</t>
+          <t>x_gcfid_ethyl_tetradecanoate_ppm</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>gcfid ethyl dodecanoate ppm</t>
+          <t>gcfid ethyl tetradecanoate ppm</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -72590,36 +72972,42 @@
         </is>
       </c>
       <c r="J64">
-        <v>0.1125</v>
+        <v>0.1575</v>
       </c>
       <c r="K64">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="L64">
-        <v>5.027298710393142</v>
+        <v>1.635576802586092</v>
       </c>
       <c r="M64">
-        <v>20.0772216256404</v>
+        <v>3.618990072475083</v>
       </c>
       <c r="N64">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="P64">
+        <v>0.003869864880731216</v>
+      </c>
+      <c r="Q64">
+        <v>0.08068493244036561</v>
+      </c>
+      <c r="R64" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R64">
+      <c r="T64">
         <v>18</v>
       </c>
     </row>
@@ -72636,12 +73024,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>x_gcfid_isoamyl_octanoate_ppm</t>
+          <t>x_gcfid_p_cresol_ppm</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>gcfid isoamyl octanoate ppm</t>
+          <t>gcfid p cresol ppm</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -72651,12 +73039,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>baja_no_directa</t>
         </is>
       </c>
       <c r="H65">
@@ -72668,36 +73056,42 @@
         </is>
       </c>
       <c r="J65">
-        <v>0.84</v>
+        <v>0.5675</v>
       </c>
       <c r="K65">
         <v>1</v>
       </c>
       <c r="L65">
-        <v>31.90975521216652</v>
+        <v>51.7218787129507</v>
       </c>
       <c r="M65">
-        <v>63.70240063977167</v>
+        <v>69.16858506759598</v>
       </c>
       <c r="N65">
-        <v>336</v>
+        <v>227</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P65">
+        <v>1</v>
+      </c>
+      <c r="Q65">
+        <v>0.7837499999999999</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R65">
+      <c r="T65">
         <v>1</v>
       </c>
     </row>
@@ -72714,12 +73108,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_dodecanoate_ppm</t>
+          <t>x_gcfid_isoamyl_octanoate_ppm</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>gcfid ethyl dodecanoate ppm</t>
+          <t>gcfid isoamyl octanoate ppm</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -72746,36 +73140,42 @@
         </is>
       </c>
       <c r="J66">
-        <v>0.7324999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="K66">
         <v>1</v>
       </c>
       <c r="L66">
-        <v>3.857973729409792</v>
+        <v>31.90975521216652</v>
       </c>
       <c r="M66">
-        <v>10.82887377263447</v>
+        <v>63.70240063977167</v>
       </c>
       <c r="N66">
-        <v>293</v>
+        <v>336</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
           <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="P66">
+        <v>0.5979225321529856</v>
+      </c>
+      <c r="Q66">
+        <v>0.7189612660764928</v>
+      </c>
+      <c r="R66" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R66">
+      <c r="T66">
         <v>2</v>
       </c>
     </row>
@@ -72792,12 +73192,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_decanoate_ppm</t>
+          <t>x_gcfid_creosol_ppm</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>gcfid ethyl decanoate ppm</t>
+          <t>gcfid creosol ppm</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -72807,12 +73207,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>otros</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>no_prioritaria</t>
         </is>
       </c>
       <c r="H67">
@@ -72824,36 +73224,42 @@
         </is>
       </c>
       <c r="J67">
-        <v>0.7175</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K67">
         <v>1</v>
       </c>
       <c r="L67">
-        <v>5.307072925764932</v>
+        <v>19.80552887023137</v>
       </c>
       <c r="M67">
-        <v>12.41315361115826</v>
+        <v>30.87548289604895</v>
       </c>
       <c r="N67">
-        <v>287</v>
+        <v>226</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P67">
+        <v>0.3522731105945253</v>
+      </c>
+      <c r="Q67">
+        <v>0.4586365552972627</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R67">
+      <c r="T67">
         <v>3</v>
       </c>
     </row>
@@ -72921,17 +73327,23 @@
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="P68">
+        <v>0.1535941133561028</v>
+      </c>
+      <c r="Q68">
+        <v>0.4330470566780514</v>
+      </c>
+      <c r="R68" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R68">
+      <c r="T68">
         <v>4</v>
       </c>
     </row>
@@ -72948,27 +73360,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>x_gcfid_isoamyl_acetate_ppm</t>
+          <t>x_gcms_aldehidos_pct</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>gcfid isoamyl acetate ppm</t>
+          <t>gcms aldehidos pct</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>GC-MS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>aldehidos_furanicos</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>no_prioritaria</t>
         </is>
       </c>
       <c r="H69">
@@ -72980,36 +73392,42 @@
         </is>
       </c>
       <c r="J69">
-        <v>0.57</v>
+        <v>0.475</v>
       </c>
       <c r="K69">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="L69">
-        <v>6.039908157474395</v>
+        <v>17.30881572091025</v>
       </c>
       <c r="M69">
-        <v>10.843151341901</v>
+        <v>30.70476203623679</v>
       </c>
       <c r="N69">
-        <v>228</v>
+        <v>190</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P69">
+        <v>0.3016035243192506</v>
+      </c>
+      <c r="Q69">
+        <v>0.3883017621596253</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>alta_en_un_modelo</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R69">
+      <c r="T69">
         <v>5</v>
       </c>
     </row>
@@ -73026,12 +73444,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>x_gcfid_p_cresol_ppm</t>
+          <t>x_gcfid_ethyl_decanoate_ppm</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>gcfid p cresol ppm</t>
+          <t>gcfid ethyl decanoate ppm</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -73041,12 +73459,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>baja_no_directa</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H70">
@@ -73058,36 +73476,42 @@
         </is>
       </c>
       <c r="J70">
-        <v>0.5675</v>
+        <v>0.7175</v>
       </c>
       <c r="K70">
         <v>1</v>
       </c>
       <c r="L70">
-        <v>51.7218787129507</v>
+        <v>5.307072925764932</v>
       </c>
       <c r="M70">
-        <v>69.16858506759598</v>
+        <v>12.41315361115826</v>
       </c>
       <c r="N70">
-        <v>227</v>
+        <v>287</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
+          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
+        </is>
+      </c>
+      <c r="P70">
+        <v>0.05803395679499337</v>
+      </c>
+      <c r="Q70">
+        <v>0.3877669783974967</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R70">
+      <c r="T70">
         <v>6</v>
       </c>
     </row>
@@ -73104,27 +73528,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>x_gcfid_creosol_ppm</t>
+          <t>x_gcms_fenolicos_pct</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>gcfid creosol ppm</t>
+          <t>gcms fenolicos pct</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>GC-MS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>no_prioritaria</t>
+          <t>baja_no_directa</t>
         </is>
       </c>
       <c r="H71">
@@ -73136,36 +73560,42 @@
         </is>
       </c>
       <c r="J71">
-        <v>0.5649999999999999</v>
+        <v>0.5175</v>
       </c>
       <c r="K71">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="L71">
-        <v>19.80552887023137</v>
+        <v>14.69536778737537</v>
       </c>
       <c r="M71">
-        <v>30.87548289604895</v>
+        <v>19.95554764888284</v>
       </c>
       <c r="N71">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="P71">
+        <v>0.2485648620363245</v>
+      </c>
+      <c r="Q71">
+        <v>0.3830324310181623</v>
+      </c>
+      <c r="R71" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R71">
+      <c r="T71">
         <v>7</v>
       </c>
     </row>
@@ -73182,12 +73612,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_octanoate_ppm</t>
+          <t>x_gcfid_ethyl_dodecanoate_ppm</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>gcfid ethyl octanoate ppm</t>
+          <t>gcfid ethyl dodecanoate ppm</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -73214,36 +73644,42 @@
         </is>
       </c>
       <c r="J72">
-        <v>0.5549999999999999</v>
+        <v>0.7324999999999999</v>
       </c>
       <c r="K72">
         <v>1</v>
       </c>
       <c r="L72">
-        <v>2.878534646197401</v>
+        <v>3.857973729409792</v>
       </c>
       <c r="M72">
-        <v>11.06716824993987</v>
+        <v>10.82887377263447</v>
       </c>
       <c r="N72">
-        <v>222</v>
+        <v>293</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
           <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
+      <c r="P72">
+        <v>0.02862518920344487</v>
+      </c>
+      <c r="Q72">
+        <v>0.3805625946017224</v>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R72">
+      <c r="T72">
         <v>8</v>
       </c>
     </row>
@@ -73260,27 +73696,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>x_gcms_fenolicos_pct</t>
+          <t>x_gcfid_isoamyl_acetate_ppm</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>gcms fenolicos pct</t>
+          <t>gcfid isoamyl acetate ppm</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>GC-MS</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>baja_no_directa</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H73">
@@ -73292,36 +73728,42 @@
         </is>
       </c>
       <c r="J73">
-        <v>0.5175</v>
+        <v>0.57</v>
       </c>
       <c r="K73">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="L73">
-        <v>14.69536778737537</v>
+        <v>6.039908157474395</v>
       </c>
       <c r="M73">
-        <v>19.95554764888284</v>
+        <v>10.843151341901</v>
       </c>
       <c r="N73">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
+          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
+        </is>
+      </c>
+      <c r="P73">
+        <v>0.07290649351742791</v>
+      </c>
+      <c r="Q73">
+        <v>0.321453246758714</v>
+      </c>
+      <c r="R73" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R73">
+      <c r="T73">
         <v>9</v>
       </c>
     </row>
@@ -73338,12 +73780,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_tetradecanoate_ppm</t>
+          <t>x_gcfid_ethyl_octanoate_ppm</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>gcfid ethyl tetradecanoate ppm</t>
+          <t>gcfid ethyl octanoate ppm</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -73370,36 +73812,42 @@
         </is>
       </c>
       <c r="J74">
-        <v>0.5175</v>
+        <v>0.5549999999999999</v>
       </c>
       <c r="K74">
         <v>1</v>
       </c>
       <c r="L74">
-        <v>3.908889917924161</v>
+        <v>2.878534646197401</v>
       </c>
       <c r="M74">
-        <v>10.41963451985467</v>
+        <v>11.06716824993987</v>
       </c>
       <c r="N74">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
           <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="P74">
+        <v>0.008747946540746359</v>
+      </c>
+      <c r="Q74">
+        <v>0.2818739732703732</v>
+      </c>
+      <c r="R74" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R74">
+      <c r="T74">
         <v>10</v>
       </c>
     </row>
@@ -73416,17 +73864,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>x_gcms_esteres_pct</t>
+          <t>x_gcfid_ethyl_tetradecanoate_ppm</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>gcms esteres pct</t>
+          <t>gcfid ethyl tetradecanoate ppm</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>GC-MS</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -73448,36 +73896,42 @@
         </is>
       </c>
       <c r="J75">
-        <v>0.48</v>
+        <v>0.5175</v>
       </c>
       <c r="K75">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="L75">
-        <v>3.106870830339224</v>
+        <v>3.908889917924161</v>
       </c>
       <c r="M75">
-        <v>7.88362653210638</v>
+        <v>10.41963451985467</v>
       </c>
       <c r="N75">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
           <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>alta_en_un_modelo</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
+      <c r="P75">
+        <v>0.02965850863280683</v>
+      </c>
+      <c r="Q75">
+        <v>0.2735792543164034</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R75">
+      <c r="T75">
         <v>11</v>
       </c>
     </row>
@@ -73494,17 +73948,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_hexadecanoate_ppm</t>
+          <t>x_gcms_esteres_pct</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>gcfid ethyl hexadecanoate ppm</t>
+          <t>gcms esteres pct</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>GC-MS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -73526,36 +73980,42 @@
         </is>
       </c>
       <c r="J76">
-        <v>0.4775</v>
+        <v>0.48</v>
       </c>
       <c r="K76">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="L76">
-        <v>2.471934450016809</v>
+        <v>3.106870830339224</v>
       </c>
       <c r="M76">
-        <v>9.194581358221063</v>
+        <v>7.88362653210638</v>
       </c>
       <c r="N76">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
           <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="P76">
+        <v>0.01338191900381726</v>
+      </c>
+      <c r="Q76">
+        <v>0.2466909595019086</v>
+      </c>
+      <c r="R76" t="inlineStr">
         <is>
           <t>alta_en_un_modelo</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R76">
+      <c r="T76">
         <v>12</v>
       </c>
     </row>
@@ -73572,27 +74032,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>x_gcms_aldehidos_pct</t>
+          <t>x_gcfid_ethyl_hexadecanoate_ppm</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>gcms aldehidos pct</t>
+          <t>gcfid ethyl hexadecanoate ppm</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>GC-MS</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>aldehidos_furanicos</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>no_prioritaria</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H77">
@@ -73604,36 +74064,42 @@
         </is>
       </c>
       <c r="J77">
-        <v>0.475</v>
+        <v>0.4775</v>
       </c>
       <c r="K77">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="L77">
-        <v>17.30881572091025</v>
+        <v>2.471934450016809</v>
       </c>
       <c r="M77">
-        <v>30.70476203623679</v>
+        <v>9.194581358221063</v>
       </c>
       <c r="N77">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
+          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
+        </is>
+      </c>
+      <c r="P77">
+        <v>0.0004961921389569221</v>
+      </c>
+      <c r="Q77">
+        <v>0.2389980960694784</v>
+      </c>
+      <c r="R77" t="inlineStr">
         <is>
           <t>alta_en_un_modelo</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R77">
+      <c r="T77">
         <v>13</v>
       </c>
     </row>
@@ -73701,17 +74167,23 @@
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>0.23625</v>
+      </c>
+      <c r="R78" t="inlineStr">
         <is>
           <t>alta_en_un_modelo</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R78">
+      <c r="T78">
         <v>14</v>
       </c>
     </row>
@@ -73728,27 +74200,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>x_folin_fenoles_totales_ug_ag_ml</t>
+          <t>x_ju_ethanol_production_g_l</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>folin fenoles totales ug ag ml</t>
+          <t>ju ethanol production g l</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Folin</t>
+          <t>JU</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>fermentacion_indirecta</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>media_indirecta</t>
         </is>
       </c>
       <c r="H79">
@@ -73760,36 +74232,42 @@
         </is>
       </c>
       <c r="J79">
-        <v>1</v>
+        <v>0.785</v>
       </c>
       <c r="K79">
         <v>1</v>
       </c>
       <c r="L79">
-        <v>13.50379654042069</v>
+        <v>41.13156196875454</v>
       </c>
       <c r="M79">
-        <v>24.81357519038591</v>
+        <v>51.67178872261947</v>
       </c>
       <c r="N79">
-        <v>400</v>
+        <v>314</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
+          <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P79">
+        <v>1</v>
+      </c>
+      <c r="Q79">
+        <v>0.8925000000000001</v>
+      </c>
+      <c r="R79" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>solo_exploratoria_ia</t>
         </is>
       </c>
-      <c r="R79">
+      <c r="T79">
         <v>1</v>
       </c>
     </row>
@@ -73806,12 +74284,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>x_ju_maltose_consumption_g_l</t>
+          <t>x_ju_ferulic_acid_conversion_index_faci_percent</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ju maltose consumption g l</t>
+          <t>ju ferulic acid conversion index faci percent</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -73838,36 +74316,42 @@
         </is>
       </c>
       <c r="J80">
-        <v>0.985</v>
+        <v>0.9275</v>
       </c>
       <c r="K80">
         <v>1</v>
       </c>
       <c r="L80">
-        <v>13.85825620525302</v>
+        <v>27.27850032490134</v>
       </c>
       <c r="M80">
-        <v>18.21196604147715</v>
+        <v>35.22784314494118</v>
       </c>
       <c r="N80">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
           <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="P80">
+        <v>0.4985819001617086</v>
+      </c>
+      <c r="Q80">
+        <v>0.7130409500808543</v>
+      </c>
+      <c r="R80" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>solo_exploratoria_ia</t>
         </is>
       </c>
-      <c r="R80">
+      <c r="T80">
         <v>2</v>
       </c>
     </row>
@@ -73884,12 +74368,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>x_ju_ferulic_acid_conversion_index_faci_percent</t>
+          <t>x_ju_final_co2_loss_g_l</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ju ferulic acid conversion index faci percent</t>
+          <t>ju final co2 loss g l</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -73916,36 +74400,42 @@
         </is>
       </c>
       <c r="J81">
-        <v>0.9275</v>
+        <v>0.875</v>
       </c>
       <c r="K81">
         <v>1</v>
       </c>
       <c r="L81">
-        <v>27.27850032490134</v>
+        <v>20.20416630870823</v>
       </c>
       <c r="M81">
-        <v>35.22784314494118</v>
+        <v>26.81576180638757</v>
       </c>
       <c r="N81">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="P81">
+        <v>0.2425230439163904</v>
+      </c>
+      <c r="Q81">
+        <v>0.5587615219581952</v>
+      </c>
+      <c r="R81" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>solo_exploratoria_ia</t>
         </is>
       </c>
-      <c r="R81">
+      <c r="T81">
         <v>3</v>
       </c>
     </row>
@@ -73962,27 +74452,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>x_ju_final_co2_loss_g_l</t>
+          <t>x_folin_fenoles_totales_ug_ag_ml</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ju final co2 loss g l</t>
+          <t>folin fenoles totales ug ag ml</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>JU</t>
+          <t>Folin</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>fermentacion_indirecta</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>media_indirecta</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H82">
@@ -73994,36 +74484,42 @@
         </is>
       </c>
       <c r="J82">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="K82">
         <v>1</v>
       </c>
       <c r="L82">
-        <v>20.20416630870823</v>
+        <v>13.50379654042069</v>
       </c>
       <c r="M82">
-        <v>26.81576180638757</v>
+        <v>24.81357519038591</v>
       </c>
       <c r="N82">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>0.5</v>
+      </c>
+      <c r="R82" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>solo_exploratoria_ia</t>
         </is>
       </c>
-      <c r="R82">
+      <c r="T82">
         <v>4</v>
       </c>
     </row>
@@ -74040,12 +74536,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>x_ju_ethanol_production_g_l</t>
+          <t>x_ju_maltose_consumption_g_l</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ju ethanol production g l</t>
+          <t>ju maltose consumption g l</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -74072,36 +74568,42 @@
         </is>
       </c>
       <c r="J83">
-        <v>0.785</v>
+        <v>0.985</v>
       </c>
       <c r="K83">
         <v>1</v>
       </c>
       <c r="L83">
-        <v>41.13156196875454</v>
+        <v>13.85825620525302</v>
       </c>
       <c r="M83">
-        <v>51.67178872261947</v>
+        <v>18.21196604147715</v>
       </c>
       <c r="N83">
-        <v>314</v>
+        <v>394</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
           <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="P83">
+        <v>0.01282983474547721</v>
+      </c>
+      <c r="Q83">
+        <v>0.4989149173727386</v>
+      </c>
+      <c r="R83" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>solo_exploratoria_ia</t>
         </is>
       </c>
-      <c r="R83">
+      <c r="T83">
         <v>5</v>
       </c>
     </row>
@@ -74118,12 +74620,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>x_gcfid_guaiacol_ppm</t>
+          <t>x_gcfid_4_ethyl_guaiacol_ppm</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>gcfid guaiacol ppm</t>
+          <t>gcfid 4 ethyl guaiacol ppm</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -74150,36 +74652,42 @@
         </is>
       </c>
       <c r="J84">
-        <v>0.9225</v>
+        <v>0.7275</v>
       </c>
       <c r="K84">
         <v>0.99</v>
       </c>
       <c r="L84">
-        <v>17.53402248779114</v>
+        <v>37.00629480951667</v>
       </c>
       <c r="M84">
-        <v>32.32363828864813</v>
+        <v>55.05258287798129</v>
       </c>
       <c r="N84">
-        <v>369</v>
+        <v>291</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="P84">
+        <v>1</v>
+      </c>
+      <c r="Q84">
+        <v>0.86375</v>
+      </c>
+      <c r="R84" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R84">
+      <c r="T84">
         <v>1</v>
       </c>
     </row>
@@ -74196,12 +74704,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>x_gcfid_p_cresol_ppm</t>
+          <t>x_gcfid_o_cresol_ppm</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>gcfid p cresol ppm</t>
+          <t>gcfid o cresol ppm</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -74228,36 +74736,42 @@
         </is>
       </c>
       <c r="J85">
-        <v>0.845</v>
+        <v>0.775</v>
       </c>
       <c r="K85">
         <v>1</v>
       </c>
       <c r="L85">
-        <v>15.64268494518121</v>
+        <v>24.7345254209672</v>
       </c>
       <c r="M85">
-        <v>20.46041263495372</v>
+        <v>42.04518748284477</v>
       </c>
       <c r="N85">
-        <v>338</v>
+        <v>310</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="P85">
+        <v>0.649892437001329</v>
+      </c>
+      <c r="Q85">
+        <v>0.7124462185006646</v>
+      </c>
+      <c r="R85" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R85">
+      <c r="T85">
         <v>2</v>
       </c>
     </row>
@@ -74274,12 +74788,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>x_gcfid_o_cresol_ppm</t>
+          <t>x_gcfid_guaiacol_ppm</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>gcfid o cresol ppm</t>
+          <t>gcfid guaiacol ppm</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -74306,36 +74820,42 @@
         </is>
       </c>
       <c r="J86">
-        <v>0.775</v>
+        <v>0.9225</v>
       </c>
       <c r="K86">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L86">
-        <v>24.7345254209672</v>
+        <v>17.53402248779114</v>
       </c>
       <c r="M86">
-        <v>42.04518748284477</v>
+        <v>32.32363828864813</v>
       </c>
       <c r="N86">
-        <v>310</v>
+        <v>369</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="P86">
+        <v>0.4444656191985679</v>
+      </c>
+      <c r="Q86">
+        <v>0.683482809599284</v>
+      </c>
+      <c r="R86" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R86">
+      <c r="T86">
         <v>3</v>
       </c>
     </row>
@@ -74352,12 +74872,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_octanoate_ppm</t>
+          <t>x_gcfid_p_cresol_ppm</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>gcfid ethyl octanoate ppm</t>
+          <t>gcfid p cresol ppm</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -74367,12 +74887,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>media_contextual</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H87">
@@ -74384,36 +74904,42 @@
         </is>
       </c>
       <c r="J87">
-        <v>0.7375</v>
+        <v>0.845</v>
       </c>
       <c r="K87">
         <v>1</v>
       </c>
       <c r="L87">
-        <v>2.319313847251581</v>
+        <v>15.64268494518121</v>
       </c>
       <c r="M87">
-        <v>9.17233425056237</v>
+        <v>20.46041263495372</v>
       </c>
       <c r="N87">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P87">
+        <v>0.3905066865552512</v>
+      </c>
+      <c r="Q87">
+        <v>0.6177533432776255</v>
+      </c>
+      <c r="R87" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R87">
+      <c r="T87">
         <v>4</v>
       </c>
     </row>
@@ -74430,27 +74956,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>x_gcfid_4_ethyl_guaiacol_ppm</t>
+          <t>x_gcms_area_valida_pct</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>gcfid 4 ethyl guaiacol ppm</t>
+          <t>gcms area valida pct</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>GC-MS</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>calidad_senal_analitica</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>baja_contextual</t>
         </is>
       </c>
       <c r="H88">
@@ -74462,36 +74988,42 @@
         </is>
       </c>
       <c r="J88">
-        <v>0.7275</v>
+        <v>0.7775</v>
       </c>
       <c r="K88">
-        <v>0.99</v>
+        <v>0.86</v>
       </c>
       <c r="L88">
-        <v>37.00629480951667</v>
+        <v>4.919758192966127</v>
       </c>
       <c r="M88">
-        <v>55.05258287798129</v>
+        <v>10.93504676509307</v>
       </c>
       <c r="N88">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P88">
+        <v>0.0845868444716619</v>
+      </c>
+      <c r="Q88">
+        <v>0.4310434222358309</v>
+      </c>
+      <c r="R88" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>prioritaria</t>
-        </is>
-      </c>
-      <c r="R88">
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
+        </is>
+      </c>
+      <c r="T88">
         <v>5</v>
       </c>
     </row>
@@ -74508,12 +75040,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>x_gcms_area_valida_pct</t>
+          <t>x_gcms_aldehidos_pct</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>gcms area valida pct</t>
+          <t>gcms aldehidos pct</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -74523,7 +75055,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>calidad_senal_analitica</t>
+          <t>aldehidos_furanicos</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -74540,36 +75072,42 @@
         </is>
       </c>
       <c r="J89">
-        <v>0.7775</v>
+        <v>0.6375</v>
       </c>
       <c r="K89">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="L89">
-        <v>4.919758192966127</v>
+        <v>7.549019384440903</v>
       </c>
       <c r="M89">
-        <v>10.93504676509307</v>
+        <v>12.78118167873715</v>
       </c>
       <c r="N89">
-        <v>311</v>
+        <v>255</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
+      <c r="P89">
+        <v>0.1595983769645344</v>
+      </c>
+      <c r="Q89">
+        <v>0.3985491884822672</v>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R89">
+      <c r="T89">
         <v>6</v>
       </c>
     </row>
@@ -74586,12 +75124,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_hexadecanoate_ppm</t>
+          <t>x_gcfid_ethyl_octanoate_ppm</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>gcfid ethyl hexadecanoate ppm</t>
+          <t>gcfid ethyl octanoate ppm</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -74618,36 +75156,42 @@
         </is>
       </c>
       <c r="J90">
-        <v>0.6575</v>
+        <v>0.7375</v>
       </c>
       <c r="K90">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="L90">
-        <v>3.386988003710015</v>
+        <v>2.319313847251581</v>
       </c>
       <c r="M90">
-        <v>13.03106524617043</v>
+        <v>9.17233425056237</v>
       </c>
       <c r="N90">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
+      <c r="P90">
+        <v>0.01039744245753168</v>
+      </c>
+      <c r="Q90">
+        <v>0.3739487212287659</v>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R90">
+      <c r="T90">
         <v>7</v>
       </c>
     </row>
@@ -74664,27 +75208,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>x_gcms_fenolicos_pct</t>
+          <t>x_gcfid_isoamyl_acetate_ppm</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>gcms fenolicos pct</t>
+          <t>gcfid isoamyl acetate ppm</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>GC-MS</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>media_contextual</t>
         </is>
       </c>
       <c r="H91">
@@ -74696,36 +75240,42 @@
         </is>
       </c>
       <c r="J91">
-        <v>0.655</v>
+        <v>0.6475</v>
       </c>
       <c r="K91">
         <v>0.87</v>
       </c>
       <c r="L91">
-        <v>4.16328339683232</v>
+        <v>5.046468962427659</v>
       </c>
       <c r="M91">
-        <v>6.660799562739052</v>
+        <v>13.5782129420379</v>
       </c>
       <c r="N91">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
+          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P91">
+        <v>0.08820184058976505</v>
+      </c>
+      <c r="Q91">
+        <v>0.3678509202948825</v>
+      </c>
+      <c r="R91" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R91">
+      <c r="T91">
         <v>8</v>
       </c>
     </row>
@@ -74742,12 +75292,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>x_gcfid_isoamyl_acetate_ppm</t>
+          <t>x_gcfid_furfural_ppm</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>gcfid isoamyl acetate ppm</t>
+          <t>gcfid furfural ppm</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -74757,12 +75307,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>aldehidos_furanicos</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>media_contextual</t>
+          <t>baja_contextual</t>
         </is>
       </c>
       <c r="H92">
@@ -74774,36 +75324,42 @@
         </is>
       </c>
       <c r="J92">
-        <v>0.6475</v>
+        <v>0.6325</v>
       </c>
       <c r="K92">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L92">
-        <v>5.046468962427659</v>
+        <v>5.22821072853028</v>
       </c>
       <c r="M92">
-        <v>13.5782129420379</v>
+        <v>12.35358468855084</v>
       </c>
       <c r="N92">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P92">
+        <v>0.09338684405671695</v>
+      </c>
+      <c r="Q92">
+        <v>0.3629434220283584</v>
+      </c>
+      <c r="R92" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R92">
+      <c r="T92">
         <v>9</v>
       </c>
     </row>
@@ -74820,12 +75376,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>x_gcms_aldehidos_pct</t>
+          <t>x_gcms_fenolicos_pct</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>gcms aldehidos pct</t>
+          <t>gcms fenolicos pct</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -74835,12 +75391,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>aldehidos_furanicos</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>baja_contextual</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H93">
@@ -74852,36 +75408,42 @@
         </is>
       </c>
       <c r="J93">
-        <v>0.6375</v>
+        <v>0.655</v>
       </c>
       <c r="K93">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="L93">
-        <v>7.549019384440903</v>
+        <v>4.16328339683232</v>
       </c>
       <c r="M93">
-        <v>12.78118167873715</v>
+        <v>6.660799562739052</v>
       </c>
       <c r="N93">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P93">
+        <v>0.06300498948737189</v>
+      </c>
+      <c r="Q93">
+        <v>0.359002494743686</v>
+      </c>
+      <c r="R93" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
+      <c r="S93" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R93">
+      <c r="T93">
         <v>10</v>
       </c>
     </row>
@@ -74898,12 +75460,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>x_gcfid_furfural_ppm</t>
+          <t>x_gcfid_ethyl_hexadecanoate_ppm</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>gcfid furfural ppm</t>
+          <t>gcfid ethyl hexadecanoate ppm</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -74913,12 +75475,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>aldehidos_furanicos</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>baja_contextual</t>
+          <t>media_contextual</t>
         </is>
       </c>
       <c r="H94">
@@ -74930,36 +75492,42 @@
         </is>
       </c>
       <c r="J94">
-        <v>0.6325</v>
+        <v>0.6575</v>
       </c>
       <c r="K94">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="L94">
-        <v>5.22821072853028</v>
+        <v>3.386988003710015</v>
       </c>
       <c r="M94">
-        <v>12.35358468855084</v>
+        <v>13.03106524617043</v>
       </c>
       <c r="N94">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
+          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P94">
+        <v>0.04085766259034398</v>
+      </c>
+      <c r="Q94">
+        <v>0.349178831295172</v>
+      </c>
+      <c r="R94" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
+      <c r="S94" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R94">
+      <c r="T94">
         <v>11</v>
       </c>
     </row>
@@ -75027,17 +75595,23 @@
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
+      <c r="P95">
+        <v>0.0001236281148683102</v>
+      </c>
+      <c r="Q95">
+        <v>0.2950618140574341</v>
+      </c>
+      <c r="R95" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr">
+      <c r="S95" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R95">
+      <c r="T95">
         <v>12</v>
       </c>
     </row>
@@ -75105,17 +75679,23 @@
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr">
+      <c r="P96">
+        <v>0.02844236402745124</v>
+      </c>
+      <c r="Q96">
+        <v>0.2917211820137256</v>
+      </c>
+      <c r="R96" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr">
+      <c r="S96" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R96">
+      <c r="T96">
         <v>13</v>
       </c>
     </row>
@@ -75183,17 +75763,23 @@
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr">
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>0.2775</v>
+      </c>
+      <c r="R97" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr">
+      <c r="S97" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R97">
+      <c r="T97">
         <v>14</v>
       </c>
     </row>
@@ -75261,17 +75847,23 @@
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
+      <c r="P98">
+        <v>0.2283463291087474</v>
+      </c>
+      <c r="Q98">
+        <v>0.3541731645543737</v>
+      </c>
+      <c r="R98" t="inlineStr">
         <is>
           <t>alta_en_un_modelo</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
+      <c r="S98" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R98">
+      <c r="T98">
         <v>15</v>
       </c>
     </row>
@@ -75288,12 +75880,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_dodecanoate_ppm</t>
+          <t>x_gcfid_isoamyl_octanoate_ppm</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>gcfid ethyl dodecanoate ppm</t>
+          <t>gcfid isoamyl octanoate ppm</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -75320,36 +75912,42 @@
         </is>
       </c>
       <c r="J99">
-        <v>0.2225</v>
+        <v>0.165</v>
       </c>
       <c r="K99">
-        <v>0.42</v>
+        <v>0.3</v>
       </c>
       <c r="L99">
-        <v>3.180067860567222</v>
+        <v>8.395861201903113</v>
       </c>
       <c r="M99">
-        <v>12.62636903882547</v>
+        <v>11.30393695570157</v>
       </c>
       <c r="N99">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="P99">
+        <v>0.1837583587544223</v>
+      </c>
+      <c r="Q99">
+        <v>0.1743791793772111</v>
+      </c>
+      <c r="R99" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
+      <c r="S99" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R99">
+      <c r="T99">
         <v>16</v>
       </c>
     </row>
@@ -75366,12 +75964,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>x_gcfid_isoamyl_octanoate_ppm</t>
+          <t>x_gcfid_ethyl_dodecanoate_ppm</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>gcfid isoamyl octanoate ppm</t>
+          <t>gcfid ethyl dodecanoate ppm</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -75398,36 +75996,42 @@
         </is>
       </c>
       <c r="J100">
-        <v>0.165</v>
+        <v>0.2225</v>
       </c>
       <c r="K100">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="L100">
-        <v>8.395861201903113</v>
+        <v>3.180067860567222</v>
       </c>
       <c r="M100">
-        <v>11.30393695570157</v>
+        <v>12.62636903882547</v>
       </c>
       <c r="N100">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
+      <c r="P100">
+        <v>0.03495433237305228</v>
+      </c>
+      <c r="Q100">
+        <v>0.1287271661865261</v>
+      </c>
+      <c r="R100" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
+      <c r="S100" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R100">
+      <c r="T100">
         <v>17</v>
       </c>
     </row>
@@ -75495,17 +76099,23 @@
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr">
+      <c r="P101">
+        <v>0.005558604395175977</v>
+      </c>
+      <c r="Q101">
+        <v>0.07152930219758799</v>
+      </c>
+      <c r="R101" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q101" t="inlineStr">
+      <c r="S101" t="inlineStr">
         <is>
           <t>baja_prioridad</t>
         </is>
       </c>
-      <c r="R101">
+      <c r="T101">
         <v>18</v>
       </c>
     </row>
@@ -75522,12 +76132,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>x_gcfid_isoamyl_octanoate_ppm</t>
+          <t>x_gcfid_p_cresol_ppm</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>gcfid isoamyl octanoate ppm</t>
+          <t>gcfid p cresol ppm</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -75537,12 +76147,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>baja_no_directa</t>
         </is>
       </c>
       <c r="H102">
@@ -75554,36 +76164,42 @@
         </is>
       </c>
       <c r="J102">
-        <v>0.86</v>
+        <v>0.5775</v>
       </c>
       <c r="K102">
         <v>0.99</v>
       </c>
       <c r="L102">
-        <v>34.37901152851589</v>
+        <v>49.34130730603035</v>
       </c>
       <c r="M102">
-        <v>64.42881147171468</v>
+        <v>70.65155166171257</v>
       </c>
       <c r="N102">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P102">
+        <v>1</v>
+      </c>
+      <c r="Q102">
+        <v>0.7887500000000001</v>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R102">
+      <c r="T102">
         <v>1</v>
       </c>
     </row>
@@ -75600,12 +76216,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_dodecanoate_ppm</t>
+          <t>x_gcfid_isoamyl_octanoate_ppm</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>gcfid ethyl dodecanoate ppm</t>
+          <t>gcfid isoamyl octanoate ppm</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -75632,36 +76248,42 @@
         </is>
       </c>
       <c r="J103">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="K103">
         <v>0.99</v>
       </c>
       <c r="L103">
-        <v>2.8996143416017</v>
+        <v>34.37901152851589</v>
       </c>
       <c r="M103">
-        <v>10.96155859546334</v>
+        <v>64.42881147171468</v>
       </c>
       <c r="N103">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
           <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr">
+      <c r="P103">
+        <v>0.6787324792545311</v>
+      </c>
+      <c r="Q103">
+        <v>0.7693662396272656</v>
+      </c>
+      <c r="R103" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q103" t="inlineStr">
+      <c r="S103" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R103">
+      <c r="T103">
         <v>2</v>
       </c>
     </row>
@@ -75678,12 +76300,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_decanoate_ppm</t>
+          <t>x_gcfid_creosol_ppm</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>gcfid ethyl decanoate ppm</t>
+          <t>gcfid creosol ppm</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -75693,12 +76315,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>otros</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>no_prioritaria</t>
         </is>
       </c>
       <c r="H104">
@@ -75710,36 +76332,42 @@
         </is>
       </c>
       <c r="J104">
-        <v>0.75</v>
+        <v>0.605</v>
       </c>
       <c r="K104">
         <v>0.99</v>
       </c>
       <c r="L104">
-        <v>3.605893699128262</v>
+        <v>21.38896741575609</v>
       </c>
       <c r="M104">
-        <v>11.72320519530452</v>
+        <v>37.68966417735824</v>
       </c>
       <c r="N104">
-        <v>300</v>
+        <v>242</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P104">
+        <v>0.3998127647577574</v>
+      </c>
+      <c r="Q104">
+        <v>0.5024063823788787</v>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R104">
+      <c r="T104">
         <v>3</v>
       </c>
     </row>
@@ -75807,17 +76435,23 @@
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
+      <c r="P105">
+        <v>0.1783162739827082</v>
+      </c>
+      <c r="Q105">
+        <v>0.4629081369913541</v>
+      </c>
+      <c r="R105" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr">
+      <c r="S105" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R105">
+      <c r="T105">
         <v>4</v>
       </c>
     </row>
@@ -75834,12 +76468,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>x_gcfid_creosol_ppm</t>
+          <t>x_gcfid_ethyl_dodecanoate_ppm</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>gcfid creosol ppm</t>
+          <t>gcfid ethyl dodecanoate ppm</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -75849,12 +76483,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>no_prioritaria</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H106">
@@ -75866,36 +76500,42 @@
         </is>
       </c>
       <c r="J106">
-        <v>0.605</v>
+        <v>0.79</v>
       </c>
       <c r="K106">
         <v>0.99</v>
       </c>
       <c r="L106">
-        <v>21.38896741575609</v>
+        <v>2.8996143416017</v>
       </c>
       <c r="M106">
-        <v>37.68966417735824</v>
+        <v>10.96155859546334</v>
       </c>
       <c r="N106">
-        <v>242</v>
+        <v>316</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr">
+          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
+        </is>
+      </c>
+      <c r="P106">
+        <v>0.002812951985177952</v>
+      </c>
+      <c r="Q106">
+        <v>0.396406475992589</v>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R106">
+      <c r="T106">
         <v>5</v>
       </c>
     </row>
@@ -75912,12 +76552,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_hexadecanoate_ppm</t>
+          <t>x_gcfid_ethyl_decanoate_ppm</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>gcfid ethyl hexadecanoate ppm</t>
+          <t>gcfid ethyl decanoate ppm</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -75944,36 +76584,42 @@
         </is>
       </c>
       <c r="J107">
-        <v>0.595</v>
+        <v>0.75</v>
       </c>
       <c r="K107">
         <v>0.99</v>
       </c>
       <c r="L107">
-        <v>2.768607573433795</v>
+        <v>3.605893699128262</v>
       </c>
       <c r="M107">
-        <v>9.862358723365517</v>
+        <v>11.72320519530452</v>
       </c>
       <c r="N107">
-        <v>238</v>
+        <v>300</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
           <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
         </is>
       </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr">
+      <c r="P107">
+        <v>0.01797804573284045</v>
+      </c>
+      <c r="Q107">
+        <v>0.3839890228664202</v>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R107">
+      <c r="T107">
         <v>6</v>
       </c>
     </row>
@@ -75990,17 +76636,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>x_gcfid_p_cresol_ppm</t>
+          <t>x_gcms_fenolicos_pct</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>gcfid p cresol ppm</t>
+          <t>gcms fenolicos pct</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>GC-MS</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -76022,36 +76668,42 @@
         </is>
       </c>
       <c r="J108">
-        <v>0.5775</v>
+        <v>0.245</v>
       </c>
       <c r="K108">
-        <v>0.99</v>
+        <v>0.37</v>
       </c>
       <c r="L108">
-        <v>49.34130730603035</v>
+        <v>23.68062753867526</v>
       </c>
       <c r="M108">
-        <v>70.65155166171257</v>
+        <v>42.25321177933573</v>
       </c>
       <c r="N108">
-        <v>231</v>
+        <v>98</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
+      <c r="P108">
+        <v>0.4490188476362901</v>
+      </c>
+      <c r="Q108">
+        <v>0.347009423818145</v>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R108">
+      <c r="T108">
         <v>7</v>
       </c>
     </row>
@@ -76068,27 +76720,27 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>x_gcfid_isoamyl_acetate_ppm</t>
+          <t>x_gcms_aldehidos_pct</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>gcfid isoamyl acetate ppm</t>
+          <t>gcms aldehidos pct</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>GC-MS</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>aldehidos_furanicos</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>no_prioritaria</t>
         </is>
       </c>
       <c r="H109">
@@ -76100,36 +76752,42 @@
         </is>
       </c>
       <c r="J109">
-        <v>0.545</v>
+        <v>0.21</v>
       </c>
       <c r="K109">
-        <v>0.99</v>
+        <v>0.37</v>
       </c>
       <c r="L109">
-        <v>5.54973460008225</v>
+        <v>24.42453771004357</v>
       </c>
       <c r="M109">
-        <v>14.06986820969265</v>
+        <v>47.1406058547369</v>
       </c>
       <c r="N109">
-        <v>218</v>
+        <v>84</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Q109" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P109">
+        <v>0.4649919429397527</v>
+      </c>
+      <c r="Q109">
+        <v>0.3374959714698764</v>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R109">
+      <c r="T109">
         <v>8</v>
       </c>
     </row>
@@ -76146,12 +76804,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_tetradecanoate_ppm</t>
+          <t>x_gcfid_isoamyl_acetate_ppm</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>gcfid ethyl tetradecanoate ppm</t>
+          <t>gcfid isoamyl acetate ppm</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -76178,36 +76836,42 @@
         </is>
       </c>
       <c r="J110">
-        <v>0.515</v>
+        <v>0.545</v>
       </c>
       <c r="K110">
         <v>0.99</v>
       </c>
       <c r="L110">
-        <v>4.93577185021401</v>
+        <v>5.54973460008225</v>
       </c>
       <c r="M110">
-        <v>11.00715624632874</v>
+        <v>14.06986820969265</v>
       </c>
       <c r="N110">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
           <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr">
+      <c r="P110">
+        <v>0.05971582155676331</v>
+      </c>
+      <c r="Q110">
+        <v>0.3023579107783817</v>
+      </c>
+      <c r="R110" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q110" t="inlineStr">
+      <c r="S110" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R110">
+      <c r="T110">
         <v>9</v>
       </c>
     </row>
@@ -76224,12 +76888,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_octanoate_ppm</t>
+          <t>x_gcfid_ethyl_hexadecanoate_ppm</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>gcfid ethyl octanoate ppm</t>
+          <t>gcfid ethyl hexadecanoate ppm</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -76256,36 +76920,42 @@
         </is>
       </c>
       <c r="J111">
-        <v>0.5024999999999999</v>
+        <v>0.595</v>
       </c>
       <c r="K111">
         <v>0.99</v>
       </c>
       <c r="L111">
-        <v>2.849962570645441</v>
+        <v>2.768607573433795</v>
       </c>
       <c r="M111">
-        <v>9.117240920538514</v>
+        <v>9.862358723365517</v>
       </c>
       <c r="N111">
-        <v>201</v>
+        <v>238</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
           <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr">
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>0.2975</v>
+      </c>
+      <c r="R111" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q111" t="inlineStr">
+      <c r="S111" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R111">
+      <c r="T111">
         <v>10</v>
       </c>
     </row>
@@ -76302,27 +76972,27 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>x_gcms_fenolicos_pct</t>
+          <t>x_gcfid_ethyl_tetradecanoate_ppm</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>gcms fenolicos pct</t>
+          <t>gcfid ethyl tetradecanoate ppm</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>GC-MS</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>baja_no_directa</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H112">
@@ -76334,36 +77004,42 @@
         </is>
       </c>
       <c r="J112">
-        <v>0.245</v>
+        <v>0.515</v>
       </c>
       <c r="K112">
-        <v>0.37</v>
+        <v>0.99</v>
       </c>
       <c r="L112">
-        <v>23.68062753867526</v>
+        <v>4.93577185021401</v>
       </c>
       <c r="M112">
-        <v>42.25321177933573</v>
+        <v>11.00715624632874</v>
       </c>
       <c r="N112">
-        <v>98</v>
+        <v>206</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr">
+          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
+        </is>
+      </c>
+      <c r="P112">
+        <v>0.0465329321517387</v>
+      </c>
+      <c r="Q112">
+        <v>0.2807664660758694</v>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R112">
+      <c r="T112">
         <v>11</v>
       </c>
     </row>
@@ -76380,17 +77056,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>x_gcms_esteres_pct</t>
+          <t>x_gcfid_ethyl_octanoate_ppm</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>gcms esteres pct</t>
+          <t>gcfid ethyl octanoate ppm</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>GC-MS</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -76412,36 +77088,42 @@
         </is>
       </c>
       <c r="J113">
-        <v>0.2225</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="K113">
-        <v>0.37</v>
+        <v>0.99</v>
       </c>
       <c r="L113">
-        <v>3.411156477655652</v>
+        <v>2.849962570645441</v>
       </c>
       <c r="M113">
-        <v>9.834478304051618</v>
+        <v>9.117240920538514</v>
       </c>
       <c r="N113">
-        <v>89</v>
+        <v>201</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
           <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr">
+      <c r="P113">
+        <v>0.001746838763454902</v>
+      </c>
+      <c r="Q113">
+        <v>0.2521234193817274</v>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R113">
+      <c r="T113">
         <v>12</v>
       </c>
     </row>
@@ -76458,12 +77140,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>x_gcms_aldehidos_pct</t>
+          <t>x_gcms_aroma_fermentativo_pct</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>gcms aldehidos pct</t>
+          <t>gcms aroma fermentativo pct</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -76473,7 +77155,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>aldehidos_furanicos</t>
+          <t>otros</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -76496,10 +77178,10 @@
         <v>0.37</v>
       </c>
       <c r="L114">
-        <v>24.42453771004357</v>
+        <v>5.892538229123437</v>
       </c>
       <c r="M114">
-        <v>47.1406058547369</v>
+        <v>12.18829389406189</v>
       </c>
       <c r="N114">
         <v>84</v>
@@ -76509,17 +77191,23 @@
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr">
+      <c r="P114">
+        <v>0.06707643477028627</v>
+      </c>
+      <c r="Q114">
+        <v>0.1385382173851431</v>
+      </c>
+      <c r="R114" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q114" t="inlineStr">
+      <c r="S114" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R114">
+      <c r="T114">
         <v>13</v>
       </c>
     </row>
@@ -76536,12 +77224,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>x_gcms_aroma_fermentativo_pct</t>
+          <t>x_gcms_esteres_pct</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>gcms aroma fermentativo pct</t>
+          <t>gcms esteres pct</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -76551,12 +77239,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>no_prioritaria</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H115">
@@ -76568,36 +77256,42 @@
         </is>
       </c>
       <c r="J115">
-        <v>0.21</v>
+        <v>0.2225</v>
       </c>
       <c r="K115">
         <v>0.37</v>
       </c>
       <c r="L115">
-        <v>5.892538229123437</v>
+        <v>3.411156477655652</v>
       </c>
       <c r="M115">
-        <v>12.18829389406189</v>
+        <v>9.834478304051618</v>
       </c>
       <c r="N115">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P115" t="inlineStr">
+          <t>Coherente: los esteres suelen asociarse a notas frutales, florales y fermentativas.</t>
+        </is>
+      </c>
+      <c r="P115">
+        <v>0.01379668578182365</v>
+      </c>
+      <c r="Q115">
+        <v>0.1181483428909118</v>
+      </c>
+      <c r="R115" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="Q115" t="inlineStr">
+      <c r="S115" t="inlineStr">
         <is>
           <t>exploratoria_target_secundario</t>
         </is>
       </c>
-      <c r="R115">
+      <c r="T115">
         <v>14</v>
       </c>
     </row>
@@ -76608,7 +77302,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -76689,15 +77383,25 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>importancia_norm_minmax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>score_combinado</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>estabilidad_consenso</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>prioridad_tesis</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ranking_consenso</t>
         </is>
@@ -76716,27 +77420,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>x_ju_maltose_consumption_g_l</t>
+          <t>x_gcfid_4_ethyl_guaiacol_ppm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ju maltose consumption g l</t>
+          <t>gcfid 4 ethyl guaiacol ppm</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JU</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>fermentacion_indirecta</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>media_indirecta</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H2">
@@ -76748,36 +77452,42 @@
         </is>
       </c>
       <c r="J2">
-        <v>0.9025000000000001</v>
+        <v>0.825</v>
       </c>
       <c r="K2">
+        <v>0.95</v>
+      </c>
+      <c r="L2">
+        <v>36.21920442171134</v>
+      </c>
+      <c r="M2">
+        <v>51.89013760839237</v>
+      </c>
+      <c r="N2">
+        <v>330</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P2">
         <v>1</v>
       </c>
-      <c r="L2">
-        <v>8.006378279693029</v>
-      </c>
-      <c r="M2">
-        <v>30.13008720070722</v>
-      </c>
-      <c r="N2">
-        <v>361</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2">
+        <v>0.9125</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R2">
+      <c r="T2">
         <v>1</v>
       </c>
     </row>
@@ -76845,17 +77555,23 @@
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3">
+        <v>0.8354031360649414</v>
+      </c>
+      <c r="Q3">
+        <v>0.8677015680324707</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>2</v>
       </c>
     </row>
@@ -76872,27 +77588,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>x_gcfid_4_ethyl_guaiacol_ppm</t>
+          <t>x_ju_maltose_consumption_g_l</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>gcfid 4 ethyl guaiacol ppm</t>
+          <t>ju maltose consumption g l</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>JU</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>fermentacion_indirecta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>media_indirecta</t>
         </is>
       </c>
       <c r="H4">
@@ -76904,36 +77620,42 @@
         </is>
       </c>
       <c r="J4">
-        <v>0.825</v>
+        <v>0.9025000000000001</v>
       </c>
       <c r="K4">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>36.21920442171134</v>
+        <v>8.006378279693029</v>
       </c>
       <c r="M4">
-        <v>51.89013760839237</v>
+        <v>30.13008720070722</v>
       </c>
       <c r="N4">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+          <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P4">
+        <v>0.2174170554261122</v>
+      </c>
+      <c r="Q4">
+        <v>0.5599585277130561</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>prioritaria</t>
-        </is>
-      </c>
-      <c r="R4">
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
+        </is>
+      </c>
+      <c r="T4">
         <v>3</v>
       </c>
     </row>
@@ -77001,17 +77723,23 @@
           <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5">
+        <v>0.2152059062818368</v>
+      </c>
+      <c r="Q5">
+        <v>0.4876029531409184</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>prioritaria</t>
-        </is>
-      </c>
-      <c r="R5">
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
+        </is>
+      </c>
+      <c r="T5">
         <v>4</v>
       </c>
     </row>
@@ -77028,27 +77756,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>x_gcfid_guaiacol_ppm</t>
+          <t>x_ju_ethanol_production_g_l</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>gcfid guaiacol ppm</t>
+          <t>ju ethanol production g l</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>JU</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>fermentacion_indirecta</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>media_indirecta</t>
         </is>
       </c>
       <c r="H6">
@@ -77060,36 +77788,42 @@
         </is>
       </c>
       <c r="J6">
-        <v>0.7524999999999999</v>
+        <v>0.6675</v>
       </c>
       <c r="K6">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="L6">
-        <v>3.178167395991517</v>
+        <v>7.855940633058448</v>
       </c>
       <c r="M6">
-        <v>4.341506335983394</v>
+        <v>27.99051361055944</v>
       </c>
       <c r="N6">
-        <v>301</v>
+        <v>267</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>prioritaria</t>
-        </is>
-      </c>
-      <c r="R6">
+          <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P6">
+        <v>0.2132441329444925</v>
+      </c>
+      <c r="Q6">
+        <v>0.4403720664722462</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
+        </is>
+      </c>
+      <c r="T6">
         <v>5</v>
       </c>
     </row>
@@ -77106,27 +77840,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>x_ju_ethanol_production_g_l</t>
+          <t>x_gcfid_guaiacol_ppm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ju ethanol production g l</t>
+          <t>gcfid guaiacol ppm</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JU</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>fermentacion_indirecta</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>media_indirecta</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H7">
@@ -77138,36 +77872,42 @@
         </is>
       </c>
       <c r="J7">
-        <v>0.6675</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="K7">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="L7">
-        <v>7.855940633058448</v>
+        <v>3.178167395991517</v>
       </c>
       <c r="M7">
-        <v>27.99051361055944</v>
+        <v>4.341506335983394</v>
       </c>
       <c r="N7">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P7">
+        <v>0.08348947683576985</v>
+      </c>
+      <c r="Q7">
+        <v>0.4179947384178849</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R7">
+      <c r="T7">
         <v>6</v>
       </c>
     </row>
@@ -77235,17 +77975,23 @@
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8">
+        <v>0.0485117596914657</v>
+      </c>
+      <c r="Q8">
+        <v>0.3455058798457329</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R8">
+      <c r="T8">
         <v>7</v>
       </c>
     </row>
@@ -77262,12 +78008,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>x_gcfid_guaiacol_ppm</t>
+          <t>x_gcfid_4_ethyl_guaiacol_ppm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>gcfid guaiacol ppm</t>
+          <t>gcfid 4 ethyl guaiacol ppm</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -77294,36 +78040,42 @@
         </is>
       </c>
       <c r="J9">
-        <v>0.9225</v>
+        <v>0.7275</v>
       </c>
       <c r="K9">
         <v>0.99</v>
       </c>
       <c r="L9">
-        <v>17.53402248779114</v>
+        <v>37.00629480951667</v>
       </c>
       <c r="M9">
-        <v>32.32363828864813</v>
+        <v>55.05258287798129</v>
       </c>
       <c r="N9">
-        <v>369</v>
+        <v>291</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>0.86375</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R9">
+      <c r="T9">
         <v>1</v>
       </c>
     </row>
@@ -77340,12 +78092,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>x_gcfid_p_cresol_ppm</t>
+          <t>x_gcfid_o_cresol_ppm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>gcfid p cresol ppm</t>
+          <t>gcfid o cresol ppm</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -77372,36 +78124,42 @@
         </is>
       </c>
       <c r="J10">
-        <v>0.845</v>
+        <v>0.775</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10">
-        <v>15.64268494518121</v>
+        <v>24.7345254209672</v>
       </c>
       <c r="M10">
-        <v>20.46041263495372</v>
+        <v>42.04518748284477</v>
       </c>
       <c r="N10">
-        <v>338</v>
+        <v>310</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10">
+        <v>0.649892437001329</v>
+      </c>
+      <c r="Q10">
+        <v>0.7124462185006646</v>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R10">
+      <c r="T10">
         <v>2</v>
       </c>
     </row>
@@ -77418,12 +78176,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>x_gcfid_o_cresol_ppm</t>
+          <t>x_gcfid_guaiacol_ppm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>gcfid o cresol ppm</t>
+          <t>gcfid guaiacol ppm</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -77450,36 +78208,42 @@
         </is>
       </c>
       <c r="J11">
-        <v>0.775</v>
+        <v>0.9225</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L11">
-        <v>24.7345254209672</v>
+        <v>17.53402248779114</v>
       </c>
       <c r="M11">
-        <v>42.04518748284477</v>
+        <v>32.32363828864813</v>
       </c>
       <c r="N11">
-        <v>310</v>
+        <v>369</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11">
+        <v>0.4444656191985679</v>
+      </c>
+      <c r="Q11">
+        <v>0.683482809599284</v>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R11">
+      <c r="T11">
         <v>3</v>
       </c>
     </row>
@@ -77496,12 +78260,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_octanoate_ppm</t>
+          <t>x_gcfid_p_cresol_ppm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>gcfid ethyl octanoate ppm</t>
+          <t>gcfid p cresol ppm</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -77511,12 +78275,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>media_contextual</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H12">
@@ -77528,36 +78292,42 @@
         </is>
       </c>
       <c r="J12">
-        <v>0.7375</v>
+        <v>0.845</v>
       </c>
       <c r="K12">
         <v>1</v>
       </c>
       <c r="L12">
-        <v>2.319313847251581</v>
+        <v>15.64268494518121</v>
       </c>
       <c r="M12">
-        <v>9.17233425056237</v>
+        <v>20.46041263495372</v>
       </c>
       <c r="N12">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P12">
+        <v>0.3905066865552512</v>
+      </c>
+      <c r="Q12">
+        <v>0.6177533432776255</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R12">
+      <c r="T12">
         <v>4</v>
       </c>
     </row>
@@ -77574,27 +78344,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>x_gcfid_4_ethyl_guaiacol_ppm</t>
+          <t>x_gcms_area_valida_pct</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>gcfid 4 ethyl guaiacol ppm</t>
+          <t>gcms area valida pct</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>GC-MS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>calidad_senal_analitica</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>baja_contextual</t>
         </is>
       </c>
       <c r="H13">
@@ -77606,36 +78376,42 @@
         </is>
       </c>
       <c r="J13">
-        <v>0.7275</v>
+        <v>0.7775</v>
       </c>
       <c r="K13">
-        <v>0.99</v>
+        <v>0.86</v>
       </c>
       <c r="L13">
-        <v>37.00629480951667</v>
+        <v>4.919758192966127</v>
       </c>
       <c r="M13">
-        <v>55.05258287798129</v>
+        <v>10.93504676509307</v>
       </c>
       <c r="N13">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P13">
+        <v>0.0845868444716619</v>
+      </c>
+      <c r="Q13">
+        <v>0.4310434222358309</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>prioritaria</t>
-        </is>
-      </c>
-      <c r="R13">
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
+        </is>
+      </c>
+      <c r="T13">
         <v>5</v>
       </c>
     </row>
@@ -77652,12 +78428,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>x_gcms_area_valida_pct</t>
+          <t>x_gcms_aldehidos_pct</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>gcms area valida pct</t>
+          <t>gcms aldehidos pct</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -77667,7 +78443,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>calidad_senal_analitica</t>
+          <t>aldehidos_furanicos</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -77684,36 +78460,42 @@
         </is>
       </c>
       <c r="J14">
-        <v>0.7775</v>
+        <v>0.6375</v>
       </c>
       <c r="K14">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="L14">
-        <v>4.919758192966127</v>
+        <v>7.549019384440903</v>
       </c>
       <c r="M14">
-        <v>10.93504676509307</v>
+        <v>12.78118167873715</v>
       </c>
       <c r="N14">
-        <v>311</v>
+        <v>255</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="P14">
+        <v>0.1595983769645344</v>
+      </c>
+      <c r="Q14">
+        <v>0.3985491884822672</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R14">
+      <c r="T14">
         <v>6</v>
       </c>
     </row>
@@ -77730,12 +78512,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_hexadecanoate_ppm</t>
+          <t>x_gcfid_ethyl_octanoate_ppm</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>gcfid ethyl hexadecanoate ppm</t>
+          <t>gcfid ethyl octanoate ppm</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -77762,36 +78544,42 @@
         </is>
       </c>
       <c r="J15">
-        <v>0.6575</v>
+        <v>0.7375</v>
       </c>
       <c r="K15">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>3.386988003710015</v>
+        <v>2.319313847251581</v>
       </c>
       <c r="M15">
-        <v>13.03106524617043</v>
+        <v>9.17233425056237</v>
       </c>
       <c r="N15">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="P15">
+        <v>0.01039744245753168</v>
+      </c>
+      <c r="Q15">
+        <v>0.3739487212287659</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R15">
+      <c r="T15">
         <v>7</v>
       </c>
     </row>
@@ -77808,27 +78596,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>x_gcms_fenolicos_pct</t>
+          <t>x_gcfid_isoamyl_acetate_ppm</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>gcms fenolicos pct</t>
+          <t>gcfid isoamyl acetate ppm</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GC-MS</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>media_contextual</t>
         </is>
       </c>
       <c r="H16">
@@ -77840,36 +78628,42 @@
         </is>
       </c>
       <c r="J16">
-        <v>0.655</v>
+        <v>0.6475</v>
       </c>
       <c r="K16">
         <v>0.87</v>
       </c>
       <c r="L16">
-        <v>4.16328339683232</v>
+        <v>5.046468962427659</v>
       </c>
       <c r="M16">
-        <v>6.660799562739052</v>
+        <v>13.5782129420379</v>
       </c>
       <c r="N16">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
+          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P16">
+        <v>0.08820184058976505</v>
+      </c>
+      <c r="Q16">
+        <v>0.3678509202948825</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R16">
+      <c r="T16">
         <v>8</v>
       </c>
     </row>
@@ -77886,12 +78680,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>x_gcfid_isoamyl_acetate_ppm</t>
+          <t>x_gcfid_furfural_ppm</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>gcfid isoamyl acetate ppm</t>
+          <t>gcfid furfural ppm</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -77901,12 +78695,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>aldehidos_furanicos</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>media_contextual</t>
+          <t>baja_contextual</t>
         </is>
       </c>
       <c r="H17">
@@ -77918,36 +78712,42 @@
         </is>
       </c>
       <c r="J17">
-        <v>0.6475</v>
+        <v>0.6325</v>
       </c>
       <c r="K17">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L17">
-        <v>5.046468962427659</v>
+        <v>5.22821072853028</v>
       </c>
       <c r="M17">
-        <v>13.5782129420379</v>
+        <v>12.35358468855084</v>
       </c>
       <c r="N17">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P17">
+        <v>0.09338684405671695</v>
+      </c>
+      <c r="Q17">
+        <v>0.3629434220283584</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R17">
+      <c r="T17">
         <v>9</v>
       </c>
     </row>
@@ -77964,12 +78764,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>x_gcms_aldehidos_pct</t>
+          <t>x_gcms_fenolicos_pct</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>gcms aldehidos pct</t>
+          <t>gcms fenolicos pct</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -77979,12 +78779,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>aldehidos_furanicos</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>baja_contextual</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H18">
@@ -77996,36 +78796,42 @@
         </is>
       </c>
       <c r="J18">
-        <v>0.6375</v>
+        <v>0.655</v>
       </c>
       <c r="K18">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="L18">
-        <v>7.549019384440903</v>
+        <v>4.16328339683232</v>
       </c>
       <c r="M18">
-        <v>12.78118167873715</v>
+        <v>6.660799562739052</v>
       </c>
       <c r="N18">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P18">
+        <v>0.06300498948737189</v>
+      </c>
+      <c r="Q18">
+        <v>0.359002494743686</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R18">
+      <c r="T18">
         <v>10</v>
       </c>
     </row>
@@ -78042,12 +78848,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>x_gcfid_furfural_ppm</t>
+          <t>x_gcfid_ethyl_hexadecanoate_ppm</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>gcfid furfural ppm</t>
+          <t>gcfid ethyl hexadecanoate ppm</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -78057,12 +78863,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>aldehidos_furanicos</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>baja_contextual</t>
+          <t>media_contextual</t>
         </is>
       </c>
       <c r="H19">
@@ -78074,36 +78880,42 @@
         </is>
       </c>
       <c r="J19">
-        <v>0.6325</v>
+        <v>0.6575</v>
       </c>
       <c r="K19">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="L19">
-        <v>5.22821072853028</v>
+        <v>3.386988003710015</v>
       </c>
       <c r="M19">
-        <v>12.35358468855084</v>
+        <v>13.03106524617043</v>
       </c>
       <c r="N19">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
+          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P19">
+        <v>0.04085766259034398</v>
+      </c>
+      <c r="Q19">
+        <v>0.349178831295172</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R19">
+      <c r="T19">
         <v>11</v>
       </c>
     </row>
@@ -78171,17 +78983,23 @@
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20">
+        <v>0.0001236281148683102</v>
+      </c>
+      <c r="Q20">
+        <v>0.2950618140574341</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R20">
+      <c r="T20">
         <v>12</v>
       </c>
     </row>
@@ -78249,17 +79067,23 @@
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21">
+        <v>0.02844236402745124</v>
+      </c>
+      <c r="Q21">
+        <v>0.2917211820137256</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R21">
+      <c r="T21">
         <v>13</v>
       </c>
     </row>
@@ -78327,17 +79151,23 @@
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0.2775</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R22">
+      <c r="T22">
         <v>14</v>
       </c>
     </row>
@@ -80424,7 +81254,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -80488,7 +81318,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -80616,7 +81446,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -80680,7 +81510,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -80744,7 +81574,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -80808,7 +81638,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -80872,7 +81702,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -80936,7 +81766,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -81192,7 +82022,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -81512,7 +82342,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
